--- a/datatransform/label/output/unextend_log.xlsx
+++ b/datatransform/label/output/unextend_log.xlsx
@@ -11297,12 +11297,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>UPF_P0016.00_ID1</t>
+          <t>UPF_P0179.00_ID1</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -11312,11 +11312,11 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 1 @ 9.3 mm)</t>
+          <t>Saved successfully (cuts: 2 @ 4.5, 3.2 mm)</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -11327,12 +11327,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>UPF_P0031.00_ID1</t>
+          <t>UPF_P0048.00_ID1</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>ICA chor</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11342,11 +11342,11 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 5.1, 4.8, 6.4 mm)</t>
+          <t>Saved successfully (cuts: 1 @ 6.6 mm)</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>UPF_P0035.00_ID1</t>
+          <t>UPF_P0031.00_ID1</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -11372,11 +11372,11 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 8.7, 7.2, 5.5 mm)</t>
+          <t>Saved successfully (cuts: 2 @ 3.5, 1.6 mm)</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -11387,12 +11387,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>UPF_P0046.00_ID1</t>
+          <t>UPF_P0148.00_ID1</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -11402,11 +11402,11 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 6.6, 6.1, 3.4, 5.2 mm)</t>
+          <t>Saved successfully (cuts: 3 @ 4.2, 3.7, 2.2 mm)</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -11417,12 +11417,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>UPF_P0048.00_ID1</t>
+          <t>UPF_P0046.00_ID1</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ICA chor</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -11432,11 +11432,11 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 1 @ 6.8 mm)</t>
+          <t>Saved successfully (cuts: 2 @ 4.9, 2.6 mm)</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -11447,12 +11447,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>UPF_P0089.00_ID2</t>
+          <t>UPF_P0208.00_ID1</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -11462,11 +11462,11 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 10.2, 4.2, 3.7 mm)</t>
+          <t>Saved successfully (cuts: 2 @ 2.9, 2.2 mm)</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -11477,12 +11477,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>UPF_P0056.00_ID1</t>
+          <t>UPF_P0230.00_ID1</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 2 @ 7.2, 6.6 mm)</t>
+          <t>Saved successfully (cuts: 2 @ 4.2, 1.5 mm)</t>
         </is>
       </c>
       <c r="E375" t="n">
@@ -11507,7 +11507,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>UPF_P0090.00_ID1</t>
+          <t>UPF_P0016.00_ID1</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -11522,11 +11522,11 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 2 @ 7.7, 6.7 mm)</t>
+          <t>Saved successfully (cuts: 3 @ 9.4, 1.8, 1.8 mm)</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -11537,12 +11537,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>UPF_P0148.00_ID1</t>
+          <t>UPF_P0035.00_ID1</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 5.9, 4.2, 3.6 mm)</t>
+          <t>Saved successfully (cuts: 3 @ 6.8, 5.5, 5.1 mm)</t>
         </is>
       </c>
       <c r="E377" t="n">
@@ -11567,7 +11567,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>UPF_P0103.00_ID1</t>
+          <t>UPF_P0056.00_ID1</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -11582,11 +11582,11 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 10.0, 4.5, 4.0, 3.6 mm)</t>
+          <t>Saved successfully (cuts: 3 @ 6.4, 6.0, 1.7 mm)</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -11597,12 +11597,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>UPF_P0208.00_ID1</t>
+          <t>UPF_P0090.00_ID1</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -11612,11 +11612,11 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Saved as-is (no cylindrical extensions found)</t>
+          <t>Saved successfully (cuts: 3 @ 3.9, 2.0, 2.1 mm)</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -11627,12 +11627,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>UPF_P0153.00_ID1</t>
+          <t>UPF_P0211.00_ID1</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ICA bif</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 5.3, 4.1, 4.0 mm)</t>
+          <t>Saved successfully (cuts: 3 @ 4.6, 2.1, 1.8 mm)</t>
         </is>
       </c>
       <c r="E380" t="n">
@@ -11657,12 +11657,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>UPF_P0179.00_ID1</t>
+          <t>UPF_P0103.00_ID1</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -11672,11 +11672,11 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 2 @ 6.0, 3.8 mm)</t>
+          <t>Saved successfully (cuts: 3 @ 3.5, 3.5, 3.3 mm)</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>UPF_P0211.00_ID1</t>
+          <t>UPF_P0089.00_ID2</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -11702,11 +11702,11 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 2 @ 4.7, 3.2 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 10.2, 2.1, 1.8, 1.6, 1.8, 1.4 mm)</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -11717,42 +11717,42 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>UPF_P0258.00_ID1</t>
+          <t>UPF_P0153.00_ID1</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>ICA bif</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Skipped</t>
+          <t>Saved</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Error: 'UnstructuredGrid' object has no attribute 'is_all_triangles'</t>
+          <t>Saved successfully (cuts: 3 @ 4.3, 2.6, 2.5 mm)</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>UPF_P0230.00_ID1</t>
+          <t>UPF_P0266.00_ID1</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -11762,11 +11762,11 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 2 @ 5.1, 4.2 mm)</t>
+          <t>Saved successfully (cuts: 1 @ 2.5 mm)</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -11777,12 +11777,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>UPF_P0261.00_ID1</t>
+          <t>UPF_P0258.00_ID1</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 2 @ 3.1, 3.3 mm)</t>
+          <t>Saved successfully (cuts: 2 @ 16.2, 1.5 mm)</t>
         </is>
       </c>
       <c r="E385" t="n">
@@ -11807,7 +11807,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>UPF_P0266.00_ID1</t>
+          <t>UPF_P0261.00_ID1</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -11822,11 +11822,11 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Saved as-is (no cylindrical extensions found)</t>
+          <t>Saved successfully (cuts: 3 @ 3.0, 2.0, 1.6 mm)</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -11852,11 +11852,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 9.1, 7.6, 4.9 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 7.1, 6.1, 3.7, 1.9, 1.6 mm)</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -11882,11 +11882,11 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.0, 9.2, 5.3, 5.1, 4.3, 5.7 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 9.4, 8.4, 5.0, 4.3, 4.3 mm)</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -11897,12 +11897,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>p092_ABMXCAMBFT4eAAgABwUQFxAR_RICA</t>
+          <t>p094_ERUeAB4WBg0SCwcbHgAABAEU</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>ICA cav</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11912,11 +11912,11 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 11.0, 10.3, 8.9, 5.0, 3.1 mm)</t>
+          <t>Saved successfully (cuts: 4 @ 12.1, 6.8, 2.3, 1.8 mm)</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -11927,12 +11927,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>p091_ABMXCAMBFT4eAAgABwUQFxAR_LICA</t>
+          <t>p103_BAgfDgUbAQAKABgGHw4bFgYZ</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11942,11 +11942,11 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.8, 11.4, 9.7, 8.1, 5.9, 3.3 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 9.1, 7.2, 5.1, 4.4, 3.3, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -11957,12 +11957,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>p094_ERUeAB4WBg0SCwcbHgAABAEU</t>
+          <t>p046_FwQADBEGGwQBGwMdHwAADBAK_RICA</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>ICA cav</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -11972,11 +11972,11 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 2 @ 13.3, 9.4 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 13.9, 13.3, 9.7, 8.7, 3.0, 2.4, 1.9, 1.6 mm)</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -11987,37 +11987,37 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>p046_FwQADBEGGwQBGwMdHwAADBAK_RICA</t>
+          <t>p109_ARQbDwQJHAANEA8BBgAABAQN</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Skipped</t>
+          <t>Saved</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Error: 'UnstructuredGrid' object has no attribute 'is_all_triangles'</t>
+          <t>Saved successfully (cuts: 5 @ 4.8, 4.5, 3.9, 3.7, 1.8 mm)</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>p097_Eg4HEwEdGw8NChMdAxQHCxcX</t>
+          <t>p092_ABMXCAMBFT4eAAgABwUQFxAR_RICA</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -12032,11 +12032,11 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 10.2, 9.2, 5.9, 5.4 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 10.1, 7.6, 4.7, 3.7, 5.1, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -12047,14 +12047,10 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>p099_FxMbBAMBHAYWFxgdGwQdDBsf</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>ICA oph</t>
-        </is>
-      </c>
+          <t>p095_EhMHDx4NAB8BEAgBFxMMFwAW_LICA</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
       <c r="C394" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -12062,11 +12058,11 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.0, 8.4, 6.9, 4.4 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 11.4, 9.7, 8.2, 4.8, 3.9, 3.3, 2.4, 2.3, 2.0 mm)</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -12077,10 +12073,14 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>p095_EhMHDx4NAB8BEAgBFxMMFwAW_LICA</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr"/>
+          <t>p097_Eg4HEwEdGw8NChMdAxQHCxcX</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>ICA oph</t>
+        </is>
+      </c>
       <c r="C395" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -12088,11 +12088,11 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 13.3, 10.4, 8.6, 6.3, 4.3, 4.1 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 10.2, 5.8, 5.6, 5.2, 1.5 mm)</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -12118,11 +12118,11 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 14.0, 8.0, 8.0, 4.5 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.3, 6.3, 5.1, 4.5, 2.4, 2.1, 2.0, 2.0 mm)</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -12133,12 +12133,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>p103_BAgfDgUbAQAKABgGHw4bFgYZ</t>
+          <t>p104_FhMbBBQNHB8BDAMLFw8IFxwd</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -12148,11 +12148,11 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 10.8, 7.4, 6.2, 4.1, 3.8 mm)</t>
+          <t>Saved successfully (cuts: 11 @ 9.6, 8.7, 5.8, 4.6, 4.0, 3.7, 3.6, 2.8, 2.1, 1.6, 1.6 mm)</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>p109_ARQbDwQJHAANEA8BBgAABAQN</t>
+          <t>p099_FxMbBAMBHAYWFxgdGwQdDBsf</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -12178,11 +12178,11 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 6.5, 5.4, 4.6, 4.0 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 11.3, 6.6, 4.9, 2.3, 2.2, 2.0, 1.5 mm)</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -12193,12 +12193,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>p104_FhMbBBQNHB8BDAMLFw8IFxwd</t>
+          <t>p117_BA4fAAMBDA4eBBUGBg4DBAYR</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -12208,11 +12208,11 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 11.0, 10.2, 8.8, 5.5, 4.9, 4.6, 4.4 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 12.4, 8.0, 4.9, 4.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -12223,12 +12223,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>p114_FxQVDRUaDBQUCQMdFRQJCRAK</t>
+          <t>p120_HA4ABB4SHR8cFwMBCA4CCgcd_RICA</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>ACA A1</t>
+          <t>ICA bif</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -12238,11 +12238,11 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 16.2, 9.8, 8.9, 7.9 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 13.2, 12.9, 9.6, 6.0, 1.9, 1.8 mm)</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -12253,12 +12253,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>p115_EgAeDBUaDAAfCAMdEAACCBAK</t>
+          <t>p091_ABMXCAMBFT4eAAgABwUQFxAR_LICA</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -12268,11 +12268,11 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 16.3, 16.1, 10.3, 8.6, 6.7 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 11.8, 7.9, 7.2, 7.1, 4.8, 1.8, 1.6 mm)</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>p117_BA4fAAMBDA4eBBUGBg4DBAYR</t>
+          <t>p124_FAQeFBMJDAQfEAUOFgQCEBYZ_RICA</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -12298,11 +12298,11 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 14.4, 9.4, 5.9, 5.4 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 13.9, 10.1, 6.9, 6.0, 1.8, 1.6 mm)</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -12313,12 +12313,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>p120_HA4ABB4SHR8cFwMBCA4CCgcd_RICA</t>
+          <t>p114_FxQVDRUaDBQUCQMdFRQJCRAK</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>ICA bif</t>
+          <t>ACA A1</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -12328,11 +12328,11 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 14.5, 14.4, 10.9, 6.8 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 13.7, 8.8, 8.5, 6.1, 3.4, 2.0 mm)</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -12343,12 +12343,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>p119_AgACCAMJAAUaGwcfGxIPFxER</t>
+          <t>p127_AwIaFhEaCAwSCwgREQkZBAcC</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -12358,11 +12358,11 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 24.8, 11.3, 5.2, 4.8, 3.8 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 10.9, 9.3, 6.2, 5.6, 2.7, 1.9, 1.5 mm)</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -12373,12 +12373,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>p121_FwgDFBUEDAgCEAMDFQgfEBAU</t>
+          <t>p119_AgACCAMJAAUaGwcfGxIPFxER</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -12388,11 +12388,11 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 14.5, 11.7, 11.2, 5.2 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 13.9, 6.7, 4.4, 3.8, 3.1, 1.6, 1.6 mm)</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -12418,11 +12418,11 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 11.0, 10.8, 8.9, 7.5, 5.7, 5.7 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 9.9, 9.5, 7.7, 5.7, 5.5, 3.7, 2.0, 1.9, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>p124_FAQeFBMJDAQfEAUOFgQCEBYZ_RICA</t>
+          <t>p121_FwgDFBUEDAgCEAMDFQgfEBAU</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -12448,11 +12448,11 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 14.9, 12.5, 7.9, 7.0 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 12.0, 10.2, 8.8, 3.9, 2.6, 2.2, 1.6 mm)</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -12463,10 +12463,14 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>p128_EggcChUaBj4=LCUuDAgADhAK_Acom</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr"/>
+          <t>p128_EggcChUaBh8aCw0KABUMDBsT_LICA</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>ICA para</t>
+        </is>
+      </c>
       <c r="C408" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -12474,11 +12478,11 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.4, 8.4, 6.2, 5.8, 4.3 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 14.7, 12.7, 7.9, 5.5, 5.1, 2.6, 1.8, 1.8 mm)</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -12489,14 +12493,10 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>p127_AwIaFhEaCAwSCwgREQkZBAcC</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>ICA oph</t>
-        </is>
-      </c>
+          <t>p128_EggcChUaBj4=LCUuDAgADhAK_Acom</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
       <c r="C409" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -12504,11 +12504,11 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 13.0, 10.8, 7.8, 5.9 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 12.4, 8.2, 6.2, 5.4, 4.1, 3.2 mm)</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -12519,10 +12519,14 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>p126_FAQBCQUbAQQAGwMcGhQdFhAL</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr"/>
+          <t>p133_AxUADhgAFwoWFxgbAA4GDRAT</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>ICA cav</t>
+        </is>
+      </c>
       <c r="C410" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -12530,11 +12534,11 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 8 @ 14.4, 12.0, 11.0, 7.9, 7.5, 6.2, 5.3, 3.3 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 9.3, 6.1, 5.7, 5.0, 2.0, 1.7 mm)</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -12545,14 +12549,10 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>p128_EggcChUaBh8aCw0KABUMDBsT_LICA</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>ICA para</t>
-        </is>
-      </c>
+          <t>p126_FAQBCQUbAQQAGwMcGhQdFhAL</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr"/>
       <c r="C411" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -12560,11 +12560,11 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 16.7, 14.1, 8.9, 5.9, 5.9 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 12.7, 8.9, 7.4, 6.7, 5.2, 5.1, 3.4, 2.2, 1.8, 1.4 mm)</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -12575,10 +12575,14 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>p134_EwkTExwNAT4DEA8IDAkPFxkd</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr"/>
+          <t>p115_EgAeDBUaDAAfCAMdEAACCBAK</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>ICA oph</t>
+        </is>
+      </c>
       <c r="C412" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -12586,11 +12590,11 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 8.9, 8.0, 6.7, 4.5 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 13.0, 12.1, 9.2, 7.7, 5.4, 3.9, 3.2, 1.6, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -12601,14 +12605,10 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>p129_ERUeAB4WBg0SCwcbHgAABAEU_LICA</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>ICA cav</t>
-        </is>
-      </c>
+          <t>p134_EwkTExwNAT4DEA8IDAkPFxkd</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
       <c r="C413" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -12616,11 +12616,11 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 16.7, 12.5, 3.1 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 7.6, 6.3, 5.5, 4.3, 2.1, 2.0 mm)</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -12631,12 +12631,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>p133_AxUADhgAFwoWFxgbAA4GDRAT</t>
+          <t>p135_FAQtEh8dAQANADkcHRQdBBEd</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>ICA cav</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -12646,11 +12646,11 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 10.7, 7.1, 6.9, 6.3 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 14.0, 9.8, 6.3, 5.4, 3.9, 3.3, 2.4, 1.4 mm)</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -12661,12 +12661,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>p135_FAQtEh8dAQANADkcHRQdBBEd</t>
+          <t>p142_AwwXAAQAFxMNCAMOBgkLFwYV</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -12676,11 +12676,11 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.8, 11.3, 9.4, 7.3, 6.7 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 10.4, 7.4, 4.8, 4.7, 4.1, 2.7, 1.8 mm)</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>p131_EwgfABQHAD4RChIHLRcLFwEG</t>
+          <t>p140_GA4LHx8RGg4KDQkWGg4XDRoB</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 17.5, 13.1, 10.3, 10.3, 8.3, 7.0, 5.8 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 15.6, 5.9, 5.5, 3.9, 2.8, 2.2, 1.8 mm)</t>
         </is>
       </c>
       <c r="E416" t="n">
@@ -12721,7 +12721,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>p137_Bg4eDRUaGw8NCgoDFxMHCwMX</t>
+          <t>p146_Ag4HCBwEFxMNChMGHg0LFwcX</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -12736,11 +12736,11 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.8, 10.8, 7.1, 7.1, 4.0 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 14.8, 8.6, 8.0, 3.0, 3.0, 2.6 mm)</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>p140_GA4LHx8RGg4KDQkWGg4XDRoB</t>
+          <t>p131_EwgfABQHAD4RChIHLRcLFwEG</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -12766,11 +12766,11 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 18.6, 11.7, 6.7, 5.1, 4.6, 8.1, 5.6 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 16.1, 12.0, 9.2, 8.4, 7.1, 6.1, 5.3, 2.1, 1.8, 1.5 mm)</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -12781,12 +12781,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>p142_AwwXAAQAFxMNCAMOBgkLFwYV</t>
+          <t>p137_Bg4eDRUaGw8NCgoDFxMHCwMX</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -12796,11 +12796,11 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.0, 8.8, 6.0, 4.8, 4.7 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 12.5, 9.0, 6.1, 5.8, 3.3, 3.4, 2.5, 2.0, 1.5 mm)</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -12811,12 +12811,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>p141_FAQfCBUaAAQNAAsGFxMcABEd</t>
+          <t>p147_Eg4cDxUeGwQNCggBFxcHABcX</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>MCA M1</t>
+          <t>ICA cav</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -12826,11 +12826,11 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 13.3, 12.0, 8.7, 6.6, 5.9, 4.7, 3.8 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 11.2, 9.9, 5.7, 5.7, 2.8, 2.1 mm)</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -12841,12 +12841,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>p136_Fw4fBAoWHQwWHwEAHwQUAhoV</t>
+          <t>p149_HQQGFQIJBxkNABIbAAAbHRgd</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>ICA para</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -12856,11 +12856,11 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.7, 9.0, 7.0, 5.4 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 13.7, 11.4, 7.6, 4.6, 2.8, 1.5 mm)</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -12871,12 +12871,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>p144_GgAREAUBFxMNBAUeBwgLFx8Z</t>
+          <t>p150_Bg4cPhcdHBUWCxgAHD4JEBsM</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -12886,11 +12886,11 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 16.3, 7.7, 7.5, 6.0, 5.7 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 11.3, 7.6, 7.4, 5.8, 2.1, 1.6 mm)</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -12901,12 +12901,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>p145_HQAAFRkWExMHDAsOABUHCBQK_RICA</t>
+          <t>p129_ERUeAB4WBg0SCwcbHgAABAEU_LICA</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>ICA cav</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -12916,11 +12916,11 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 15.7, 14.0, 11.9, 7.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 13.4, 11.6, 8.8, 2.7, 3.7, 1.9, 1.7, 1.4 mm)</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -12931,12 +12931,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>p146_Ag4HCBwEFxMNChMGHg0LFwcX</t>
+          <t>p144_GgAREAUBFxMNBAUeBwgLFx8Z</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -12946,11 +12946,11 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 17.7, 11.0, 10.9, 4.4 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 9.8, 7.2, 5.1, 4.9, 4.8, 4.9, 2.0 mm)</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -12961,14 +12961,10 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>p147_Eg4cDxUeGwQNCggBFxcHABcX</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>ICA cav</t>
-        </is>
-      </c>
+          <t>p151_FAAtDQUSDAAsCRMVFgAxCQAC</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
       <c r="C425" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -12976,11 +12972,11 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 13.9, 11.5, 9.2, 8.1 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 9.6, 7.6, 6.6, 4.2, 1.7, 1.7, 1.6 mm)</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -12991,7 +12987,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>p149_HQQGFQIJBxkNABIbAAAbHRgd</t>
+          <t>p145_HQAAFRkWExMHDAsOABUHCBQK_RICA</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -13006,11 +13002,11 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 16.3, 12.2, 8.7, 6.0 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 14.2, 11.8, 11.0, 6.7, 2.0, 1.6 mm)</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -13021,10 +13017,14 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>p151_FAAtDQUSDAAsCRMVFgAxCQAC</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr"/>
+          <t>p152_AAQABAoWFxMWHxYKAAQUFRAK</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>ICA oph</t>
+        </is>
+      </c>
       <c r="C427" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13032,11 +13032,11 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 10.5, 9.6, 9.2, 5.0 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 8.9, 6.1, 4.7, 2.8, 2.8, 2.3, 1.8 mm)</t>
         </is>
       </c>
       <c r="E427" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -13047,14 +13047,10 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>p150_Bg4cPhcdHBUWCxgAHD4JEBsM</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>ICA oph</t>
-        </is>
-      </c>
+          <t>p154_HRQeDRUaDBQfCQMdHxQCCRAK</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
       <c r="C428" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13062,11 +13058,11 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.4, 9.2, 8.9, 6.3 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 12.3, 9.9, 9.7, 7.6, 4.3, 1.8, 1.7 mm)</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -13077,14 +13073,10 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>p152_AAQABAoWFxMWHxYKAAQUFRAK</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>ICA oph</t>
-        </is>
-      </c>
+          <t>p153_AwAeAA4JHgAABAoOAQACBAYZ_LICA</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr"/>
       <c r="C429" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13092,11 +13084,11 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.4, 10.7, 6.8, 3.4 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 12.9, 9.8, 9.1, 8.2, 7.4, 3.7, 3.0 mm)</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -13107,12 +13099,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>p157_EgAYExEFGx8SDxQOHwgMBB8K</t>
+          <t>p141_FAQfCBUaAAQNAAsGFxMcABEd</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>MCA M1</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -13122,11 +13114,11 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 14.5, 12.6, 10.2, 8.1 mm)</t>
+          <t>Saved successfully (cuts: 13 @ 9.8, 9.7, 7.3, 6.0, 5.1, 4.4, 3.8, 3.3, 1.8, 1.8, 1.7, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -13137,10 +13129,14 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>p154_HRQeDRUaDBQfCQMdHxQCCRAK</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr"/>
+          <t>p157_EgAYExEFGx8SDxQOHwgMBB8K</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>ICA oph</t>
+        </is>
+      </c>
       <c r="C431" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13148,11 +13144,11 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.2, 11.2, 11.1, 8.3, 5.3 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 11.5, 10.3, 7.9, 6.8, 3.0, 1.6 mm)</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -13163,12 +13159,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>p158_Fg4bEgMJER8cDBUcEwIIChwL</t>
+          <t>p136_Fw4fBAoWHQwWHwEAHwQUAhoV</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>ICA para</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -13178,11 +13174,11 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.0, 9.4, 8.8, 6.6, 4.7 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 11.2, 7.4, 5.8, 4.2, 2.6, 2.5, 2.2, 1.4 mm)</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -13193,7 +13189,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>p153_AwAeAA4JHgAABAoOAQACBAYZ_LICA</t>
+          <t>p162_AwkTAxEGGx8bBAQOHAgdDRQa</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
@@ -13204,11 +13200,11 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 14.3, 12.9, 10.2, 9.2, 8.7, 4.1 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 10.8, 8.3, 4.8, 3.2, 2.3, 2.3, 2.2 mm)</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -13219,14 +13215,10 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>p159_FRIGExEMEx8AERQOFgALFgEK</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>ICA oph</t>
-        </is>
-      </c>
+          <t>p163_EwkdAxESDAkcBwcVEQkBBxQC</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
       <c r="C434" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13234,11 +13226,11 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.3, 11.6, 9.7, 4.1 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 15.3, 9.0, 4.9, 3.6, 3.3, 1.5 mm)</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -13249,12 +13241,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>p160_GhQGGxUcDBQHHwMbGBQaHxAM</t>
+          <t>p159_FRIGExEMEx8AERQOFgALFgEK</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>ICA cav</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -13264,11 +13256,11 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.9, 10.7, 10.4, 7.7, 4.4 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 10.7, 10.0, 8.1, 3.5, 2.5, 1.9, 1.5 mm)</t>
         </is>
       </c>
       <c r="E435" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -13279,10 +13271,14 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>p162_AwkTAxEGGx8bBAQOHAgdDRQa</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr"/>
+          <t>p158_Fg4bEgMJER8cDBUcEwIIChwL</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>MCA bif</t>
+        </is>
+      </c>
       <c r="C436" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13290,11 +13286,11 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.4, 9.9, 7.5, 3.9 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 12.6, 7.7, 7.0, 5.4, 4.1, 2.0 mm)</t>
         </is>
       </c>
       <c r="E436" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -13305,12 +13301,12 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>p161_FBMdGw4aHRsXFwkVFhMBHxEK</t>
+          <t>p160_GhQGGxUcDBQHHwMbGBQaHxAM</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>ICA cav</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -13320,11 +13316,11 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.0, 13.7, 11.8, 9.0, 7.5 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 12.6, 10.1, 8.5, 5.5, 3.7, 2.1, 1.7, 1.6, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E437" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -13335,10 +13331,14 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>p165_Gw4aDwQHAhENCg4BBg4eFR4X</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr"/>
+          <t>p168_EgQVCAMAHQ0fDBgKFQgdDRoU</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>ICA cav</t>
+        </is>
+      </c>
       <c r="C438" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.6, 12.3, 10.0, 7.6, 5.8, 4.9 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 11.4, 8.1, 7.2, 3.3, 2.1, 1.7 mm)</t>
         </is>
       </c>
       <c r="E438" t="n">
@@ -13361,14 +13361,10 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>p166_AwAcBgUBHAQHEQ8REw8JEBwW</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>ICA pcom</t>
-        </is>
-      </c>
+          <t>p169_FgAeAhkGFw0fDBgOHgIHCxAU</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr"/>
       <c r="C439" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13376,11 +13372,11 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 16.5, 11.9, 8.6 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 11.1, 8.6, 6.8, 6.0, 5.0, 3.1, 2.3, 2.1, 1.7 mm)</t>
         </is>
       </c>
       <c r="E439" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -13391,10 +13387,14 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>p163_EwkdAxESDAkcBwcVEQkBBxQC</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr"/>
+          <t>p167_FxMTDxQCFwAdGxQOHAUEABQW</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>ICA oph</t>
+        </is>
+      </c>
       <c r="C440" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13402,11 +13402,11 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 17.9, 9.7, 5.8, 4.1 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 14.1, 13.2, 8.1, 5.0, 2.7, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E440" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -13417,14 +13417,10 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>p167_FxMTDxQCFwAdGxQOHAUEABQW</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>ICA oph</t>
-        </is>
-      </c>
+          <t>p304_HQQLDREGDAQKCQcBHwQXCRQW_LICA</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
       <c r="C441" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13432,11 +13428,11 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 15.9, 14.1, 9.2, 5.6 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 7.9, 6.9, 6.4, 4.3, 3.3, 2.8, 2.9, 1.7 mm)</t>
         </is>
       </c>
       <c r="E441" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -13447,12 +13443,12 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>p168_EgQVCAMAHQ0fDBgKFQgdDRoU</t>
+          <t>p174_FAQtDhwBBAQaFwcRFz4BCRwO</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>ICA cav</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -13462,11 +13458,11 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.5, 9.3, 8.0, 5.8 mm)</t>
+          <t>Saved successfully (cuts: 3 @ 15.4, 12.4, 8.4 mm)</t>
         </is>
       </c>
       <c r="E442" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -13477,10 +13473,14 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>p170_EgQABhUaDAQBAgMdEAQcAhAK</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr"/>
+          <t>p309_BggTAhMHCB8aBAUMHRsYDBQb</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>AComA</t>
+        </is>
+      </c>
       <c r="C443" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13488,7 +13488,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.2, 8.5, 8.5, 6.9, 6.3 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 8.3, 6.1, 5.1, 4.9, 2.1 mm)</t>
         </is>
       </c>
       <c r="E443" t="n">
@@ -13503,7 +13503,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>p171_EgAWBAIcAQIbABQREwULFwEL</t>
+          <t>p170_EgQABhUaDAQBAgMdEAQcAhAK</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -13514,11 +13514,11 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.4, 11.9, 10.1, 4.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 11.2, 7.6, 7.5, 5.7, 5.3, 1.9, 1.6, 1.6 mm)</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -13529,10 +13529,14 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>p169_FgAeAhkGFw0fDBgOHgIHCxAU</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr"/>
+          <t>p306_HQIbDwQHAQkNBg8BBg4dDRgb</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>MCA M1</t>
+        </is>
+      </c>
       <c r="C445" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13540,11 +13544,11 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 14.5, 13.0, 12.6, 7.5, 6.0, 3.3 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 7.5, 6.5, 5.2, 5.1, 3.8 mm)</t>
         </is>
       </c>
       <c r="E445" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -13555,14 +13559,10 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>p172_AAAeAAoSHQ8aGwcDExsUChsR</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>ICA oph</t>
-        </is>
-      </c>
+          <t>p305_HQQLDREGDAQKCQcBHwQXCRQW_RICA</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr"/>
       <c r="C446" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13570,11 +13570,11 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 16.1, 11.5, 10.6, 8.0, 6.5, 6.2 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 11.1, 5.3, 4.6, 4.4, 4.3, 3.2, 3.5, 1.8, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E446" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -13585,12 +13585,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>p174_FAQtDhwBBAQaFwcRFz4BCRwO</t>
+          <t>p308_GA4BFRUcBg0WFxgAARULEQEU</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>PICA</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -13600,11 +13600,11 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 15.8, 13.7, 9.1 mm)</t>
+          <t>Saved successfully (cuts: 4 @ 6.8, 6.6, 4.9, 1.7 mm)</t>
         </is>
       </c>
       <c r="E447" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -13615,10 +13615,14 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>p304_HQQLDREGDAQKCQcBHwQXCRQW_LICA</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr"/>
+          <t>p307_GxQdDxUGDBQcCwMBGRQBCxAW</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>PICA</t>
+        </is>
+      </c>
       <c r="C448" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13626,11 +13630,11 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.8, 7.7, 7.3, 5.7, 4.2, 3.4 mm)</t>
+          <t>Saved successfully (cuts: 4 @ 13.7, 7.2, 5.3, 5.3 mm)</t>
         </is>
       </c>
       <c r="E448" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -13641,14 +13645,10 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>p306_HQIbDwQHAQkNBg8BBg4dDRgb</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>MCA M1</t>
-        </is>
-      </c>
+          <t>p165_Gw4aDwQHAhENCg4BBg4eFR4X</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
       <c r="C449" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13656,11 +13656,11 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 9.3, 8.8, 6.7, 5.9, 5.5 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 11.9, 10.7, 6.4, 6.2, 5.0, 3.9, 1.9, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -13671,10 +13671,14 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>p305_HQQLDREGDAQKCQcBHwQXCRQW_RICA</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr"/>
+          <t>p166_AwAcBgUBHAQHEQ8REw8JEBwW</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>ICA pcom</t>
+        </is>
+      </c>
       <c r="C450" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13682,11 +13686,11 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 13.7, 7.6, 5.6, 5.1, 4.9, 4.0 mm)</t>
+          <t>Saved successfully (cuts: 4 @ 13.6, 8.6, 6.7, 3.8 mm)</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -13697,12 +13701,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>p307_GxQdDxUGDBQcCwMBGRQBCxAW</t>
+          <t>p161_FBMdGw4aHRsXFwkVFhMBHxEK</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>PICA</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -13712,11 +13716,11 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 18.2, 7.8, 5.8 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 13.4, 12.5, 6.3, 6.0, 4.8, 2.2, 2.1, 2.0, 1.4 mm)</t>
         </is>
       </c>
       <c r="E451" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -13727,12 +13731,12 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>p308_GA4BFRUcBg0WFxgAARULEQEU</t>
+          <t>p311_GwgcBQUWGw8XEA0GHAUbDhwW</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>PICA</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -13742,11 +13746,11 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 12.2, 7.8, 5.5 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 7.1, 6.1, 6.0, 3.7, 2.5, 2.3, 1.5 mm)</t>
         </is>
       </c>
       <c r="E452" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -13757,12 +13761,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>p309_BggTAhMHCB8aBAUMHRsYDBQb</t>
+          <t>p312_BggcEh8GDAgdFgkBBAgAFhoW</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -13772,11 +13776,11 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 13.6, 7.8, 7.4, 6.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 13.1, 6.0, 5.6, 4.1, 3.6, 2.0, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E453" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -13802,11 +13806,11 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 11.4, 9.5, 8.1 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 9.6, 6.8, 5.2, 2.5, 2.2, 2.1 mm)</t>
         </is>
       </c>
       <c r="E454" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -13817,12 +13821,12 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>p311_GwgcBQUWGw8XEA0GHAUbDhwW</t>
+          <t>p314_Fw0TEgMNCx8fBBUcFxgJCRQL</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -13832,11 +13836,11 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 9.2, 8.0, 7.3, 4.5, 3.7 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 10.8, 7.1, 6.1, 4.9, 2.1, 1.7, 1.7 mm)</t>
         </is>
       </c>
       <c r="E455" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -13847,12 +13851,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>p312_BggcEh8GDAgdFgkBBAgAFhoW</t>
+          <t>p172_AAAeAAoSHQ8aGwcDExsUChsR</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -13862,11 +13866,11 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 15.6, 7.1, 6.9, 5.1, 4.5, 6.0 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 15.3, 9.9, 7.2, 7.0, 6.4, 5.2, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E456" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -13892,11 +13896,11 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.3, 6.6, 6.4, 4.8, 4.3 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 9.0, 5.9, 3.8, 3.8, 3.7, 2.2, 2.2 mm)</t>
         </is>
       </c>
       <c r="E457" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -13907,14 +13911,10 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>p314_Fw0TEgMNCx8fBBUcFxgJCRQL</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>AComA</t>
-        </is>
-      </c>
+          <t>p171_EgAWBAIcAQIbABQREwULFwEL</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr"/>
       <c r="C458" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -13922,11 +13922,11 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.6, 9.6, 6.9, 5.9 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 11.9, 7.5, 7.4, 4.3, 2.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -13937,12 +13937,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>p315_FREbDxURDBEaCwMWFxEHCxAB</t>
+          <t>p322_BA4ACBEGGz4jLCUuDA4cDBQW</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>PICA</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.1, 7.9, 7.2, 6.6 mm)</t>
+          <t>Saved successfully (cuts: 4 @ 10.7, 9.5, 7.8, 2.3 mm)</t>
         </is>
       </c>
       <c r="E459" t="n">
@@ -13967,12 +13967,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>p317_HRQeDRUaDBQfCQMdHxQCCRAK</t>
+          <t>p320_FAQRAAIMFxcSBhgKEQAcARAO</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>PICA</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -13982,11 +13982,11 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.8, 12.2, 10.4, 8.2 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 8.2, 4.5, 4.0, 3.8, 1.5, 1.4 mm)</t>
         </is>
       </c>
       <c r="E460" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -13997,12 +13997,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>p316_Ag4WExkPBwQJGwkLAAgJEBAC</t>
+          <t>p321_BA4ACBEGGx8cFw8OHAgaCgcR_BA</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -14012,11 +14012,11 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 10.7, 9.9, 7.8, 7.0, 6.4 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 10.8, 6.3, 6.0, 5.3, 5.2, 3.1, 2.2, 1.5, 1.5 mm)</t>
         </is>
       </c>
       <c r="E461" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -14027,12 +14027,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>p320_FAQRAAIMFxcSBhgKEQAcARAO</t>
+          <t>p317_HRQeDRUaDBQfCQMdHxQCCRAK</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>PICA</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -14042,11 +14042,11 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 12.1, 6.3, 5.3 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 11.3, 10.5, 6.7, 6.6, 2.1, 1.8, 1.7 mm)</t>
         </is>
       </c>
       <c r="E462" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>p319_EQ8WGxEFEx8dARwOHwAPCxEC</t>
+          <t>p316_Ag4WExkPBwQJGwkLAAgJEBAC</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -14072,11 +14072,11 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 15.7, 13.7, 10.8, 8.4, 7.9, 5.7 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 8.7, 7.0, 6.8, 5.5, 5.4, 2.8, 1.8, 1.6 mm)</t>
         </is>
       </c>
       <c r="E463" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -14087,12 +14087,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>p321_BA4ACBEGGx8cFw8OHAgaCgcR_BA</t>
+          <t>p315_FREbDxURDBEaCwMWFxEHCxAB</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -14102,11 +14102,11 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.2, 8.7, 7.9, 6.6, 5.9 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 7.6, 6.9, 6.4, 5.1, 5.0, 1.6 mm)</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -14117,12 +14117,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>p322_BA4ACBEGGz4jLCUuDA4cDBQW</t>
+          <t>p331_Ag4BBAINHBINChUKAAQAFgcX</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>PICA</t>
+          <t>ICA bif</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -14132,11 +14132,11 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 12.3, 11.7, 8.3 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 12.4, 10.0, 8.4, 7.4, 3.3, 1.7 mm)</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -14147,12 +14147,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>p324_GgARAhEaFh8SBgUOAAUEBBYb</t>
+          <t>p325_GwAcBA4JHAQYBAgKGQAAAB4Z</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -14162,11 +14162,11 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 10.8, 6.9, 6.8, 5.3, 4.1 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 14.5, 8.7, 8.4, 7.1, 4.6, 1.8, 1.8 mm)</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -14177,10 +14177,14 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>p326_HA4HDR8dDA4GCQkaHg4bCRoN</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr"/>
+          <t>p327_BggeDREGBwQFBBgGHg0PCwAd</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>ICA pcom</t>
+        </is>
+      </c>
       <c r="C467" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -14188,11 +14192,11 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 24.3, 9.7, 7.5, 4.9 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 9.3, 8.0, 5.4, 5.2, 3.8, 1.9, 1.6 mm)</t>
         </is>
       </c>
       <c r="E467" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -14203,12 +14207,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>p323_HggVBhUEGx8aAgEKHggADBIf</t>
+          <t>p334_FwAHBRkGDAAGAQ8BFQAbARwW</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -14218,11 +14222,11 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 17.8, 10.3, 9.9, 9.4, 6.9 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 14.4, 8.4, 5.8, 5.6, 3.7, 3.8, 2.5, 1.6 mm)</t>
         </is>
       </c>
       <c r="E468" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -14233,14 +14237,10 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>p325_GwAcBA4JHAQYBAgKGQAAAB4Z</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>AComA</t>
-        </is>
-      </c>
+          <t>p326_HA4HDR8dDA4GCQkaHg4bCRoN</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
       <c r="C469" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -14248,7 +14248,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 18.6, 11.1, 9.8, 9.6 mm)</t>
+          <t>Saved successfully (cuts: 4 @ 16.6, 9.1, 6.0, 4.3 mm)</t>
         </is>
       </c>
       <c r="E469" t="n">
@@ -14263,12 +14263,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>p327_BggeDREGBwQFBBgGHg0PCwAd</t>
+          <t>p324_GgARAhEaFh8SBgUOAAUEBBYb</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -14278,11 +14278,11 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 10.4, 9.9, 6.1, 5.5, 5.2 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 9.8, 5.9, 4.9, 4.6, 3.4, 2.2, 1.8, 1.6 mm)</t>
         </is>
       </c>
       <c r="E470" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -14308,11 +14308,11 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 13.9, 11.8, 7.0, 3.1 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.4, 9.9, 6.0, 2.5, 1.8, 2.0, 1.8, 1.6 mm)</t>
         </is>
       </c>
       <c r="E471" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>p330_FAQDFBkMBh8WFBMGFhUKAAQN</t>
+          <t>p319_EQ8WGxEFEx8dARwOHwAPCxEC</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -14338,11 +14338,11 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 13.2, 9.3, 5.9, 5.6, 4.5, 4.3, 4.0 mm)</t>
+          <t>Saved successfully (cuts: 11 @ 13.0, 11.9, 8.2, 7.7, 7.0, 4.6, 3.3, 1.8, 1.6, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E472" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>p333_AhQdDQMWBw4fFhQaHQ0dFwAX</t>
+          <t>p338_FwQdExcNAR8WChQIFxIJABoK_RICA</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -14368,11 +14368,11 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 15.1, 10.7, 9.2, 6.7, 5.2, 4.6 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 12.4, 6.3, 5.7, 4.3, 3.1 mm)</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -14383,12 +14383,12 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>p331_Ag4BBAINHBINChUKAAQAFgcX</t>
+          <t>p330_FAQDFBkMBh8WFBMGFhUKAAQN</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>ICA bif</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -14398,11 +14398,11 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 15.0, 10.4, 9.6, 9.4 mm)</t>
+          <t>Saved successfully (cuts: 12 @ 10.6, 7.8, 5.2, 4.8, 3.7, 3.6, 3.4, 2.2, 2.2, 1.9, 1.7, 1.7 mm)</t>
         </is>
       </c>
       <c r="E474" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -14413,12 +14413,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>p334_FwAHBRkGDAAGAQ8BFQAbARwW</t>
+          <t>p336_EwkTDxUSDAkSCwMVEQkPCxAC</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -14428,11 +14428,11 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 16.5, 11.7, 7.0, 6.3, 4.9 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 13.0, 7.3, 5.9, 4.3, 3.2, 3.1, 2.7 mm)</t>
         </is>
       </c>
       <c r="E475" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>p336_EwkTDxUSDAkSCwMVEQkPCxAC</t>
+          <t>p323_HggVBhUEGx8aAgEKHggADBIf</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -14458,11 +14458,11 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 15.1, 12.2, 6.8, 5.0, 4.6, 4.3, 3.1 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 14.0, 8.9, 8.1, 8.0, 4.7, 4.3, 2.2, 2.0, 1.8 mm)</t>
         </is>
       </c>
       <c r="E476" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -14488,11 +14488,11 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.0, 6.2, 4.9, 4.6, 4.0 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 10.9, 5.5, 4.1, 4.0, 3.7, 1.7, 1.4, 1.4 mm)</t>
         </is>
       </c>
       <c r="E477" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -14503,12 +14503,12 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>p338_FwQdExcNAR8WChQIFxIJABoK_RICA</t>
+          <t>p340_HRQUFRkLDBQVEQ8MHxQIERwb</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -14518,11 +14518,11 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.3, 9.1, 7.6, 5.3, 3.4 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 12.0, 9.5, 7.4, 6.4, 5.4, 5.0, 4.7, 2.4, 1.6 mm)</t>
         </is>
       </c>
       <c r="E478" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -14548,11 +14548,11 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 17.3, 10.8, 6.3, 5.6 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 14.8, 6.4, 5.6, 4.7, 1.9, 2.8, 1.9, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E479" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -14563,12 +14563,12 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>p341_HRQcEhMADBQdFgUHHxQAFhYQ</t>
+          <t>p333_AhQdDQMWBw4fFhQaHQ0dFwAX</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -14578,11 +14578,11 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 16.2, 9.2, 6.7, 6.0, 4.8 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 13.5, 7.7, 6.1, 5.7, 4.4, 3.4, 2.0, 1.9, 1.4 mm)</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -14593,12 +14593,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>p342_AAgcCR83HgQaEQMRGw8GCioU</t>
+          <t>p351_HQQaCA4NGggeAA4GHwQGDBgd</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -14608,11 +14608,11 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 16.1, 9.1, 8.5, 6.0, 4.3, 3.8 mm)</t>
+          <t>Saved successfully (cuts: 4 @ 10.2, 5.5, 4.8, 2.4 mm)</t>
         </is>
       </c>
       <c r="E481" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>p340_HRQUFRkLDBQVEQ8MHxQIERwb</t>
+          <t>p342_AAgcCR83HgQaEQMRGw8GCioU</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -14638,11 +14638,11 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 16.4, 11.2, 9.3, 8.1, 7.9, 5.6 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 13.3, 8.1, 6.4, 5.1, 4.0, 3.4, 2.3, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E482" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -14653,12 +14653,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>p343_AgARBB4NBh8SBgMBFxUcBBYd</t>
+          <t>p345_HRQeDRUaDBQfCQMdHxQCCRAK</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>ICA bif</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -14668,11 +14668,11 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 19.5, 7.8, 7.6, 5.4, 4.4, 4.0 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 15.5, 12.0, 8.2, 6.6, 5.7, 4.1, 2.2, 1.5 mm)</t>
         </is>
       </c>
       <c r="E483" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -14683,14 +14683,10 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>p344_AA4UBxUcDA4VAwMbAg4IAxAM</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>MCA bif</t>
-        </is>
-      </c>
+          <t>p349_GwgeCBMWGw0aBg0GHggNDhwU</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr"/>
       <c r="C484" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -14698,7 +14694,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 19.6, 11.4, 7.2, 6.7, 5.4, 5.3 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 12.4, 8.7, 6.8, 5.6, 2.3, 2.2 mm)</t>
         </is>
       </c>
       <c r="E484" t="n">
@@ -14728,11 +14724,11 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.1, 14.0, 7.8, 5.7, 4.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.2, 12.0, 6.5, 4.3, 4.3, 2.4, 1.9, 1.6 mm)</t>
         </is>
       </c>
       <c r="E485" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -14743,12 +14739,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>p347_FAQEBBwJCx8WEwMDExgKAAMd</t>
+          <t>p344_AA4UBxUcDA4VAwMbAg4IAxAM</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -14758,11 +14754,11 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.8, 10.5, 6.6, 5.5, 5.2, 5.0 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 15.9, 6.9, 5.8, 4.5, 4.0, 3.2, 4.3, 2.6, 1.6, 1.6 mm)</t>
         </is>
       </c>
       <c r="E486" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -14773,12 +14769,12 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>p345_HRQeDRUaDBQfCQMdHxQCCRAK</t>
+          <t>p341_HRQcEhMADBQdFgUHHxQAFhYQ</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>ICA bif</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -14788,11 +14784,11 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 17.1, 13.8, 9.0, 8.1, 6.1, 4.7 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.0, 7.0, 4.5, 3.8, 3.6, 3.0, 1.9, 1.4 mm)</t>
         </is>
       </c>
       <c r="E487" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -14803,12 +14799,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>p348_Eg4VDwUMEx8cAggaFgAMChIW</t>
+          <t>p343_AgARBB4NBh8SBgMBFxUcBBYd</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>MCA M1</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -14818,11 +14814,11 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.5, 8.0, 6.7, 4.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 11.0, 6.5, 6.2, 5.0, 3.9, 3.3, 4.9, 1.7 mm)</t>
         </is>
       </c>
       <c r="E488" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -14833,10 +14829,14 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>p349_GwgeCBMWGw0aBg0GHggNDhwU</t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr"/>
+          <t>p353_EggcChUaBh8aCw0KABUMDBsT_RICA</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>MCA bif</t>
+        </is>
+      </c>
       <c r="C489" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -14844,11 +14844,11 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 13.8, 10.3, 8.2, 7.9 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.8, 7.1, 5.7, 5.5, 4.7, 4.4, 1.8, 1.8 mm)</t>
         </is>
       </c>
       <c r="E489" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -14859,12 +14859,12 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>p351_HQQaCA4NGggeAA4GHwQGDBgd</t>
+          <t>p348_Eg4VDwUMEx8cAggaFgAMChIW</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>MCA M1</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -14874,11 +14874,11 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 13.0, 7.2, 5.9 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 10.8, 6.2, 4.7, 3.7, 2.1, 1.9, 1.9, 1.7 mm)</t>
         </is>
       </c>
       <c r="E490" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -14889,12 +14889,12 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>p354_ERMIAA4aCAASFxwOExMUBBQK</t>
+          <t>p352_FggEAAoWGxcSHwAGBAAUAxwO</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>ICA chor</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -14904,11 +14904,11 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 15.5, 12.9, 6.8, 6.7, 4.6, 4.6 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 16.6, 7.5, 7.0, 5.7, 5.7, 3.8, 3.6, 2.6, 2.4 mm)</t>
         </is>
       </c>
       <c r="E491" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>p352_FggEAAoWGxcSHwAGBAAUAxwO</t>
+          <t>p347_FAQEBBwJCx8WEwMDExgKAAMd</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -14934,11 +14934,11 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 18.5, 10.5, 8.5, 7.9, 6.6, 4.4, 3.9 mm)</t>
+          <t>Saved successfully (cuts: 12 @ 9.6, 6.9, 4.8, 4.7, 4.5, 2.7, 2.5, 2.3, 2.0, 1.6, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E492" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>p353_EggcChUaBh8aCw0KABUMDBsT_RICA</t>
+          <t>p361_HgABERkGAQoaGwccAggAFh4R_RMCA</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -14964,11 +14964,11 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 14.9, 8.6, 6.3, 6.1, 5.2, 5.2 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 17.7, 10.1, 9.1, 6.2, 6.1, 2.1, 2.0 mm)</t>
         </is>
       </c>
       <c r="E493" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -14979,12 +14979,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>p355_EhMXFQ4aFxURFwMbEBMLERcK</t>
+          <t>p363_BhQRCh8eGwINEAUEHRcHBgMN</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 13.5, 13.3, 10.7, 9.8, 9.0, 8.7, 5.9 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 10.4, 7.4, 6.7, 4.7, 3.3, 1.9, 1.6 mm)</t>
         </is>
       </c>
       <c r="E494" t="n">
@@ -15024,11 +15024,11 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.4, 11.7, 8.1, 7.3, 6.3 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 11.5, 10.6, 7.3, 6.4, 5.4, 2.6, 1.8, 1.7 mm)</t>
         </is>
       </c>
       <c r="E495" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -15039,12 +15039,12 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>p357_EhMTDxQHHB8BBAgLHQ8MFxQW</t>
+          <t>p354_ERMIAA4aCAASFxwOExMUBBQK</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>ICA chor</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -15054,11 +15054,11 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 13.2, 12.5, 9.9, 9.9, 6.7, 4.6 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 11.7, 10.5, 5.1, 4.2, 4.2, 3.8, 4.4, 3.4, 1.8, 1.6 mm)</t>
         </is>
       </c>
       <c r="E496" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -15069,12 +15069,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>p356_EwAcCAYNCB8SCw8ZFxsNBBsR</t>
+          <t>p355_EhMXFQ4aFxURFwMbEBMLERcK</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -15084,11 +15084,11 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 15.8, 15.1, 10.2, 8.5, 8.2, 3.5 mm)</t>
+          <t>Saved successfully (cuts: 11 @ 12.5, 10.7, 9.0, 8.5, 8.1, 7.7, 5.6, 3.0, 1.9, 1.9, 1.6 mm)</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -15099,12 +15099,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>p359_ExMXGA4aFxgQFwMWERMLHBYK</t>
+          <t>p356_EwAcCAYNCB8SCw8ZFxsNBBsR</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -15114,11 +15114,11 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 18.4, 13.7, 10.2, 10.2, 9.4, 5.3, 3.6 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 14.0, 9.6, 9.2, 7.6, 7.0, 3.1, 6.0, 2.7, 2.3, 1.5 mm)</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -15129,12 +15129,12 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>p363_BhQRCh8eGwINEAUEHRcHBgMN</t>
+          <t>p365_FxQGHwUcFRQHAhMbFRQaAgAM</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.6, 9.5, 7.7, 5.6, 3.6, 5.4 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 12.7, 6.8, 6.3, 5.8, 2.2, 1.9 mm)</t>
         </is>
       </c>
       <c r="E499" t="n">
@@ -15159,12 +15159,12 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>p361_HgABERkGAQoaGwccAggAFh4R_RMCA</t>
+          <t>p367_Eg0TDxMHDA0SCwUAEA0PCxYX</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>ICA para</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -15174,11 +15174,11 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 20.2, 11.4, 11.3, 8.3, 6.9 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 12.0, 7.8, 7.8, 6.8, 2.2, 1.7 mm)</t>
         </is>
       </c>
       <c r="E500" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -15189,10 +15189,14 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>p360_AA4RCR8GDA4QDQkBAg4NDRoW</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr"/>
+          <t>p359_ExMXGA4aFxgQFwMWERMLHBYK</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>AComA</t>
+        </is>
+      </c>
       <c r="C501" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -15200,11 +15204,11 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 20.7, 14.3, 12.5, 12.0, 7.9, 7.3 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 14.6, 9.4, 8.8, 8.6, 8.1, 4.8, 3.4, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E501" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -15215,14 +15219,10 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>p362_HgABERkGAQoaGwccAggAFh4R_LMCA</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>MCA bif</t>
-        </is>
-      </c>
+          <t>p368_HA4CBAMWHREWFgoAAgQdCRoI</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr"/>
       <c r="C502" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 15.9, 9.7, 8.9, 6.8, 5.2, 5.2, 5.0 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 13.6, 10.5, 6.3, 5.5, 4.8, 2.2, 1.8 mm)</t>
         </is>
       </c>
       <c r="E502" t="n">
@@ -15245,7 +15245,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>p365_FxQGHwUcFRQHAhMbFRQaAgAM</t>
+          <t>p357_EhMTDxQHHB8BBAgLHQ8MFxQW</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -15260,11 +15260,11 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 14.0, 8.4, 7.6, 7.4 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 12.5, 10.6, 8.6, 8.3, 5.8, 4.0, 2.2, 2.1, 1.6, 1.6 mm)</t>
         </is>
       </c>
       <c r="E503" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -15275,12 +15275,12 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>p367_Eg0TDxMHDA0SCwUAEA0PCxYX</t>
+          <t>p369_GAAHEgMEFxMNBBMcAQ0LFx0Z</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>ICA para</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -15290,11 +15290,11 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 15.1, 9.2, 8.7, 8.1 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 12.4, 11.7, 8.6, 7.2, 2.2, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E504" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -15305,12 +15305,12 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>p364_FQYVEg4PFRIWAgEcFwYJFhAf</t>
+          <t>p366_EQ8RAAkWHAISHAcBEQAXBBsb</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>ICA bif</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -15320,11 +15320,11 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 8 @ 20.6, 12.1, 8.9, 7.5, 5.8, 5.5, 3.3, 4.8 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 12.9, 10.1, 8.2, 8.1, 7.9, 6.4, 2.0, 1.9, 1.9, 1.5 mm)</t>
         </is>
       </c>
       <c r="E505" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -15335,12 +15335,12 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>p369_GAAHEgMEFxMNBBMcAQ0LFx0Z</t>
+          <t>p362_HgABERkGAQoaGwccAggAFh4R_LMCA</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -15350,11 +15350,11 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 13.7, 13.0, 9.0, 8.7 mm)</t>
+          <t>Saved successfully (cuts: 12 @ 12.9, 8.7, 7.2, 6.0, 4.8, 4.5, 3.5, 2.4, 2.3, 1.4, 1.4, 1.4 mm)</t>
         </is>
       </c>
       <c r="E506" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -15365,10 +15365,14 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>p368_HA4CBAMWHREWFgoAAgQdCRoI</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr"/>
+          <t>p364_FQYVEg4PFRIWAgEcFwYJFhAf</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>AComA</t>
+        </is>
+      </c>
       <c r="C507" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -15376,11 +15380,11 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.6, 11.8, 10.3, 6.5, 5.3 mm)</t>
+          <t>Saved successfully (cuts: 12 @ 13.7, 10.0, 7.4, 6.0, 5.0, 4.8, 2.4, 6.3, 1.8, 1.6, 1.5, 1.4 mm)</t>
         </is>
       </c>
       <c r="E507" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -15391,14 +15395,10 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>p366_EQ8RAAkWHAISHAcBEQAXBBsb</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>ICA bif</t>
-        </is>
-      </c>
+          <t>p376_AA0TDwQBBAQSEBgDEw8aDAMd_RMCA</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr"/>
       <c r="C508" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -15406,11 +15406,11 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 14.5, 11.7, 9.5, 9.3, 9.2, 7.6 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 15.2, 11.3, 9.5, 8.8, 7.6, 6.9, 1.9, 1.5 mm)</t>
         </is>
       </c>
       <c r="E508" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -15421,12 +15421,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>p370_HxcXEx4NCx8FABQBFxgBExAK</t>
+          <t>p373_EwAWAB4WEwUSCwUOFgAABhQc</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>ICA bif</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -15436,11 +15436,11 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 17.1, 10.8, 10.2, 9.7 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 15.4, 8.1, 7.5, 5.9, 2.2, 1.4 mm)</t>
         </is>
       </c>
       <c r="E509" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -15451,14 +15451,10 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>p372_EwkXExkQDAkWFw8XEQkLFxwA</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>ICA pcom</t>
-        </is>
-      </c>
+          <t>p371_HQAICBwEFx8SHw8DHgQDBA8R</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr"/>
       <c r="C510" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -15466,11 +15462,11 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.8, 9.4, 8.5, 4.4, 3.5 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 13.6, 9.4, 9.4, 7.7, 7.6, 4.1, 3.1, 2.8, 1.9, 1.7 mm)</t>
         </is>
       </c>
       <c r="E510" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -15481,10 +15477,14 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>p371_HQAICBwEFx8SHw8DHgQDBA8R</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr"/>
+          <t>p372_EwkXExkQDAkWFw8XEQkLFxwA</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>ICA pcom</t>
+        </is>
+      </c>
       <c r="C511" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -15492,11 +15492,11 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 14.3, 11.6, 11.3, 9.3, 8.4, 4.8 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 10.4, 7.8, 7.1, 3.4, 2.6, 2.0, 1.6, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E511" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -15507,12 +15507,12 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>p373_EwAWAB4WEwUSCwUOFgAABhQc</t>
+          <t>p370_HxcXEx4NCx8FABQBFxgBExAK</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>ICA bif</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -15522,11 +15522,11 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 17.3, 10.0, 8.6, 6.4 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 15.0, 9.3, 9.0, 7.0, 2.2, 2.1, 2.0 mm)</t>
         </is>
       </c>
       <c r="E512" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -15537,12 +15537,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>p374_EwkXDxEeGwQBGw4KHAAYDBAK</t>
+          <t>p378_HA4ABB4SHR8cFwMBCA4CCgcd_LICA</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>ICA bif</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -15552,11 +15552,11 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 15.8, 13.1, 12.1, 9.1 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 12.0, 8.5, 6.6, 4.1, 1.9, 1.6 mm)</t>
         </is>
       </c>
       <c r="E513" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -15567,14 +15567,10 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>p378_HA4ABB4SHR8cFwMBCA4CCgcd_LICA</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>ICA bif</t>
-        </is>
-      </c>
+          <t>p360_AA4RCR8GDA4QDQkBAg4NDRoW</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr"/>
       <c r="C514" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -15582,11 +15578,11 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.9, 9.6, 7.4, 4.7 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 15.8, 10.5, 9.8, 8.2, 6.6, 4.6, 4.6, 4.0, 2.4, 1.4 mm)</t>
         </is>
       </c>
       <c r="E514" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -15597,10 +15593,14 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>p375_AwIaBB4DFw0NBg4KHAoLCQYb</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr"/>
+          <t>p374_EwkXDxEeGwQBGw4KHAAYDBAK</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>AComA</t>
+        </is>
+      </c>
       <c r="C515" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -15608,11 +15608,11 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.9, 10.9, 10.2, 10.1, 4.4 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 12.4, 11.1, 11.1, 7.0, 3.6, 1.8, 1.6 mm)</t>
         </is>
       </c>
       <c r="E515" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -15623,12 +15623,12 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>p377_AA0TDwQBBAQSEBgDEw8aDAMd_LMCA</t>
+          <t>p382_GAALDgoWExgcHw4OCw4UDRQB</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>PICA</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -15638,11 +15638,11 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.1, 11.6, 11.3, 11.0, 6.7, 3.1 mm)</t>
+          <t>Saved successfully (cuts: 4 @ 16.6, 7.7, 2.4, 1.7 mm)</t>
         </is>
       </c>
       <c r="E516" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -15653,10 +15653,14 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>p376_AA0TDwQBBAQSEBgDEw8aDAMd_RMCA</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr"/>
+          <t>p380_FwgeDRkHCB8aCQoGHRsJDBkU_RICA</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>MCA M1</t>
+        </is>
+      </c>
       <c r="C517" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -15664,11 +15668,11 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 16.7, 13.2, 10.7, 10.7, 9.1, 8.3, 5.3 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 8.6, 7.5, 7.0, 5.9, 1.5 mm)</t>
         </is>
       </c>
       <c r="E517" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -15679,12 +15683,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>p380_FwgeDRkHCB8aCQoGHRsJDBkU_RICA</t>
+          <t>p377_AA0TDwQBBAQSEBgDEw8aDAMd_LMCA</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>MCA M1</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -15694,11 +15698,11 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 10.5, 9.2, 8.1, 6.1 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 10.6, 10.4, 9.3, 7.9, 4.5, 2.7, 2.1, 2.0, 1.7 mm)</t>
         </is>
       </c>
       <c r="E518" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -15709,14 +15713,10 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>p382_GAALDgoWExgcHw4OCw4UDRQB</t>
-        </is>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>PICA</t>
-        </is>
-      </c>
+          <t>p375_AwIaBB4DFw0NBg4KHAoLCQYb</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr"/>
       <c r="C519" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -15724,11 +15724,11 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 19.0, 9.2, 5.2 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 12.2, 9.7, 9.1, 7.8, 3.4, 1.6 mm)</t>
         </is>
       </c>
       <c r="E519" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -15739,12 +15739,12 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>p381_EQ0eBBcaHR8fCQMIAA4PCRkd</t>
+          <t>p386_BAQLEgMBFxMNAB8cAQgLFwEd</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>ICA hypo</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 18.6, 12.6, 11.6, 10.6, 6.7, 5.3, 6.2 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 11.1, 8.9, 7.3, 4.8, 1.6, 1.5, 1.5 mm)</t>
         </is>
       </c>
       <c r="E520" t="n">
@@ -15769,14 +15769,10 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>p385_FAQeFBMJDAQfEAUOFgQCEBYZ</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>AComA</t>
-        </is>
-      </c>
+          <t>p384_FAQeBAQaExsNAAoKBhMPHxEd</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr"/>
       <c r="C521" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -15784,11 +15780,11 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 18.1, 15.9, 14.1, 12.8, 3.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 11.5, 8.5, 7.2, 4.5, 3.4, 2.5, 2.2, 2.1 mm)</t>
         </is>
       </c>
       <c r="E521" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -15799,7 +15795,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>p379_EwAfEREGEx8SCBYOHAANBBgI_LICA</t>
+          <t>p389_HQAAFRkWExMHDAsOABUHCBQK</t>
         </is>
       </c>
       <c r="B522" t="inlineStr"/>
@@ -15810,7 +15806,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 8 @ 18.8, 15.4, 9.7, 9.2, 8.5, 6.6, 6.2, 5.7 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 11.0, 7.7, 6.3, 4.4, 2.4, 1.8, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E522" t="n">
@@ -15825,7 +15821,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>p384_FAQeBAQaExsNAAoKBhMPHxEd</t>
+          <t>p383_HQ4ABB4HDA4BAAgAHw4cABsX</t>
         </is>
       </c>
       <c r="B523" t="inlineStr"/>
@@ -15836,11 +15832,11 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.7, 10.0, 8.2, 5.6, 5.1, 5.0 mm)</t>
+          <t>Saved successfully (cuts: 13 @ 11.1, 7.5, 6.9, 6.6, 4.6, 4.4, 4.1, 3.9, 1.9, 3.4, 2.2, 2.0, 1.9 mm)</t>
         </is>
       </c>
       <c r="E523" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -15851,10 +15847,14 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>p383_HQ4ABB4HDA4BAAgAHw4cABsX</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr"/>
+          <t>p387_AxQWAB4WBwUSCxUaFgAAFgAc</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>AComA</t>
+        </is>
+      </c>
       <c r="C524" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -15862,7 +15862,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 8 @ 14.1, 8.7, 8.5, 6.0, 5.7, 5.2, 5.1, 4.7 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 14.1, 9.6, 6.2, 5.5, 2.5, 2.6, 1.5, 1.5 mm)</t>
         </is>
       </c>
       <c r="E524" t="n">
@@ -15877,12 +15877,12 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>p386_BAQLEgMBFxMNAB8cAQgLFwEd</t>
+          <t>p393_HQgeDRUcDAgfCQMbHwgCCRAM</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>ICA hypo</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -15892,11 +15892,11 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.5, 10.0, 8.4, 5.2 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 13.2, 9.2, 4.8, 4.3, 4.0, 3.0, 2.4, 2.2, 1.8, 1.7 mm)</t>
         </is>
       </c>
       <c r="E525" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>p387_AxQWAB4WBwUSCxUaFgAAFgAc</t>
+          <t>p391_GgAcPhQdLQIbAAgKDAAAOhEN</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -15922,11 +15922,11 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 16.1, 11.8, 7.5, 6.6, 3.5 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.8, 8.3, 8.3, 7.7, 6.3, 4.2, 1.5, 1.4 mm)</t>
         </is>
       </c>
       <c r="E526" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>p389_HQAAFRkWExMHDAsOABUHCBQK</t>
+          <t>p392_FBQGEwUNHh8GERQaFw0KEAEK</t>
         </is>
       </c>
       <c r="B527" t="inlineStr"/>
@@ -15948,11 +15948,11 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 13.7, 10.7, 7.4, 4.9 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 13.5, 9.1, 7.4, 4.1, 2.5, 2.2, 1.8, 1.6 mm)</t>
         </is>
       </c>
       <c r="E527" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -15963,12 +15963,12 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>p388_Ag4BEhUcDA4AFgMbAA4dFhAM</t>
+          <t>p385_FAQeFBMJDAQfEAUOFgQCEBYZ</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -15978,11 +15978,11 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 13.0, 12.2, 9.6, 5.7, 5.3, 6.0 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 14.6, 10.8, 8.4, 7.3, 3.3, 4.1, 2.7, 1.4 mm)</t>
         </is>
       </c>
       <c r="E528" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>p390_FQ0QEwkLGhUNCQQdCwIGERAU</t>
+          <t>p379_EwAfEREGEx8SCBYOHAANBBgI_LICA</t>
         </is>
       </c>
       <c r="B529" t="inlineStr"/>
@@ -16004,11 +16004,11 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 12.0, 11.2, 10.1, 10.1, 7.9, 6.4, 5.4 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 12.3, 10.6, 8.3, 7.4, 6.4, 5.8, 5.2, 4.8, 3.1, 2.1 mm)</t>
         </is>
       </c>
       <c r="E529" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -16019,10 +16019,14 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>p392_FBQGEwUNHh8GERQaFw0KEAEK</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr"/>
+          <t>p381_EQ0eBBcaHR8fCQMIAA4PCRkd</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>AComA</t>
+        </is>
+      </c>
       <c r="C530" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -16030,11 +16034,11 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.7, 11.6, 11.0, 6.5, 3.1 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 13.7, 11.1, 10.0, 7.4, 5.5, 4.5, 2.8, 2.3, 1.7, 1.6 mm)</t>
         </is>
       </c>
       <c r="E530" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -16045,12 +16049,12 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>p393_HQgeDRUcDAgfCQMbHwgCCRAM</t>
+          <t>p394_Eg4EAAkWHRcSHAQABAAXBxoO</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -16060,11 +16064,11 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 16.7, 11.3, 7.2, 5.4, 5.1, 3.7 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 10.9, 9.0, 8.7, 5.3, 5.1, 2.0, 1.6 mm)</t>
         </is>
       </c>
       <c r="E531" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -16075,7 +16079,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>p391_GgAcPhQdLQIbAAgKDAAAOhEN</t>
+          <t>p396_EQIRDgIMGw8cGwUMHRMKDBsX</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -16090,11 +16094,11 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 13.5, 10.6, 9.9, 8.8, 8.4, 4.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.1, 11.0, 8.3, 8.2, 5.7, 2.4, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E532" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -16105,14 +16109,10 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>p394_Eg4EAAkWHRcSHAQABAAXBxoO</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>MCA bif</t>
-        </is>
-      </c>
+          <t>p395_BAkdDBEbAQQHGw4AHwAdFhAM</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr"/>
       <c r="C533" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -16120,11 +16120,11 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 11.5, 10.7, 10.6, 6.3, 6.0 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 17.2, 10.9, 8.6, 7.1, 6.4, 4.3, 2.2, 2.1, 1.5 mm)</t>
         </is>
       </c>
       <c r="E533" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -16135,12 +16135,12 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>p396_EQIRDgIMGw8cGwUMHRMKDBsX</t>
+          <t>p405_HRQABRERDBQBAQcWHxQcARQB</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>PCA P1-P2</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.0, 12.9, 9.9, 9.5, 7.0 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 9.1, 5.0, 4.3, 4.0, 1.7 mm)</t>
         </is>
       </c>
       <c r="E534" t="n">
@@ -16165,12 +16165,12 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>p397_GBQVAAMWBwYSFg4aFQAdDQAf</t>
+          <t>p408_FwABEhUaDAAAFgMdFQAdFhAK</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>PICA</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -16180,11 +16180,11 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.4, 8.7, 8.4, 6.9, 5.3, 4.8 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 16.2, 5.8, 4.9, 2.9, 2.6 mm)</t>
         </is>
       </c>
       <c r="E535" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -16195,10 +16195,14 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>p395_BAkdDBEbAQQHGw4AHwAdFhAM</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr"/>
+          <t>p397_GBQVAAMWBwYSFg4aFQAdDQAf</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>MCA bif</t>
+        </is>
+      </c>
       <c r="C536" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -16206,11 +16210,11 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 18.0, 15.0, 10.9, 10.1, 6.9, 4.9 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 11.0, 8.0, 5.9, 5.7, 4.4, 4.3, 2.8, 1.9, 1.5 mm)</t>
         </is>
       </c>
       <c r="E536" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -16221,12 +16225,12 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>p400_AgAWDgYJHA4FDAUREwUBExQW</t>
+          <t>p388_Ag4BEhUcDA4AFgMbAA4dFhAM</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -16236,11 +16240,11 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.9, 14.2, 9.8, 9.2, 5.4 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 11.4, 8.4, 6.0, 5.2, 4.3, 3.2, 2.1, 1.7, 1.7 mm)</t>
         </is>
       </c>
       <c r="E537" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -16251,7 +16255,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>p398_AAgRAAIMLQYGDAEBHQ8QDBYZ_LICA</t>
+          <t>p399_AAgRAAIMLQYGDAEBHQ8QDBYZ_RICA</t>
         </is>
       </c>
       <c r="B538" t="inlineStr"/>
@@ -16262,11 +16266,11 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 8 @ 17.1, 14.3, 13.4, 12.0, 10.2, 5.7, 5.0, 4.5 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 12.7, 8.3, 8.2, 7.2, 6.5, 3.1, 3.0, 2.7, 1.7 mm)</t>
         </is>
       </c>
       <c r="E538" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -16277,10 +16281,14 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>p401_GwAAAhgNAB8SFwUHFxMFBAcb</t>
-        </is>
-      </c>
-      <c r="B539" t="inlineStr"/>
+          <t>p402_GA4BFRUcBg0WFxgAARULEQEU_BA</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>BA tip</t>
+        </is>
+      </c>
       <c r="C539" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -16288,11 +16296,11 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.1, 9.9, 7.2, 7.0, 5.3 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 10.8, 7.2, 6.5, 6.4, 6.4, 6.2, 6.0, 2.9, 2.4 mm)</t>
         </is>
       </c>
       <c r="E539" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -16303,10 +16311,14 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>p399_AAgRAAIMLQYGDAEBHQ8QDBYZ_RICA</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr"/>
+          <t>p407_FxQbDRwNBh8GDAoDFxUJEBwU</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>MCA bif</t>
+        </is>
+      </c>
       <c r="C540" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -16314,11 +16326,11 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 15.0, 11.0, 9.8, 8.2, 7.3, 4.5 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 11.1, 6.8, 5.0, 4.6, 4.4, 1.5, 1.5 mm)</t>
         </is>
       </c>
       <c r="E540" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -16329,12 +16341,12 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>p402_GA4BFRUcBg0WFxgAARULEQEU_BA</t>
+          <t>p410_EwAAExkHDAABFw8AEQAcFxwX</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>ICA bif</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -16344,11 +16356,11 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 8 @ 14.0, 8.9, 8.9, 7.7, 7.5, 7.1, 6.8, 4.5 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 13.3, 6.9, 6.5, 4.5, 1.8, 1.8 mm)</t>
         </is>
       </c>
       <c r="E541" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -16359,14 +16371,10 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>p405_HRQABRERDBQBAQcWHxQcARQB</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>PCA P1-P2</t>
-        </is>
-      </c>
+          <t>p404_EgAAAxUSExUNBBQNFxsPERcZ</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr"/>
       <c r="C542" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -16374,11 +16382,11 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 11.7, 6.5, 6.3, 5.4 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 11.1, 6.4, 4.9, 4.8, 4.6, 3.3, 3.2, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E542" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -16389,7 +16397,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>p404_EgAAAxUSExUNBBQNFxsPERcZ</t>
+          <t>p401_GwAAAhgNAB8SFwUHFxMFBAcb</t>
         </is>
       </c>
       <c r="B543" t="inlineStr"/>
@@ -16400,7 +16408,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 12.3, 8.5, 5.7, 5.6, 5.1, 4.2, 3.9 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 11.2, 8.4, 6.1, 5.9, 5.0, 2.3, 1.8 mm)</t>
         </is>
       </c>
       <c r="E543" t="n">
@@ -16415,12 +16423,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>p407_FxQbDRwNBh8GDAoDFxUJEBwU</t>
+          <t>p409_AggGEhMAExMXGw8bAQIGBAcc</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>ICA chor</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -16430,11 +16438,11 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.1, 7.0, 5.8, 5.5, 5.3 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 13.5, 9.4, 9.4, 3.8, 3.2, 1.7, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E544" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -16445,14 +16453,10 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>p406_FwgeDRkHCB8aCQoGHRsJDBkU_LICA</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>MCA bif</t>
-        </is>
-      </c>
+          <t>p390_FQ0QEwkLGhUNCQQdCwIGERAU</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr"/>
       <c r="C545" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -16460,11 +16464,11 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 8.5, 8.2, 7.8, 7.2, 6.3, 5.2 mm)</t>
+          <t>Saved successfully (cuts: 12 @ 8.9, 8.8, 8.6, 8.6, 5.7, 3.4, 3.1, 3.3, 2.1, 1.7, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E545" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -16475,12 +16479,12 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>p403_BAkXCB4cCB8bAA8BBhsaDRAR</t>
+          <t>p400_AgAWDgYJHA4FDAUREwUBExQW</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -16490,11 +16494,11 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 19.3, 9.1, 8.5, 7.6, 6.1, 6.0, 4.2 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.8, 9.2, 8.7, 8.6, 3.4, 2.3, 2.2, 1.5 mm)</t>
         </is>
       </c>
       <c r="E546" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -16505,12 +16509,12 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>p408_FwABEhUaDAAAFgMdFQAdFhAK</t>
+          <t>p411_HBQcAAIMGx8GCwcdFggCEBsZ_LICA</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>PICA</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -16520,11 +16524,11 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 19.5, 9.2, 5.5 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 16.5, 9.1, 6.4, 5.9, 5.5, 5.0, 4.0, 1.4 mm)</t>
         </is>
       </c>
       <c r="E547" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -16535,12 +16539,12 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>p410_EwAAExkHDAABFw8AEQAcFxwX</t>
+          <t>p406_FwgeDRkHCB8aCQoGHRsJDBkU_LICA</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>ICA bif</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -16550,11 +16554,11 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 14.5, 8.2, 7.5, 5.0 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 7.9, 6.3, 5.7, 4.6, 4.6, 4.3, 1.8, 1.6, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E548" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -16580,11 +16584,11 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 11.6, 10.0, 9.7, 5.9, 5.1 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 10.2, 8.3, 8.1, 4.6, 4.3, 2.3, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E549" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -16595,14 +16599,10 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>p409_AggGEhMAExMXGw8bAQIGBAcc</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>ICA chor</t>
-        </is>
-      </c>
+          <t>p398_AAgRAAIMLQYGDAEBHQ8QDBYZ_LICA</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr"/>
       <c r="C550" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -16610,11 +16610,11 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.9, 11.4, 10.7, 5.5, 4.4 mm)</t>
+          <t>Saved successfully (cuts: 12 @ 15.7, 13.5, 10.9, 9.8, 9.2, 4.8, 4.1, 3.8, 2.7, 2.2, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E550" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -16625,12 +16625,12 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>p413_GgAREAUBFxMNBAUeBwgLFx8Z_RICA</t>
+          <t>p415_FhMTBh4BFxMWGxQOFQ8HAAcd_RICA</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>PeriA</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -16640,11 +16640,11 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.3, 8.2, 7.6, 7.5, 5.2 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 14.9, 7.3, 5.0, 3.7, 2.1, 2.4, 2.1, 1.8, 1.5 mm)</t>
         </is>
       </c>
       <c r="E551" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>p411_HBQcAAIMGx8GCwcdFggCEBsZ_LICA</t>
+          <t>p413_GgAREAUBFxMNBAUeBwgLFx8Z_RICA</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -16670,7 +16670,7 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 18.1, 9.9, 7.8, 7.2, 5.6, 5.6, 4.7 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 9.8, 6.7, 5.4, 5.1, 3.8, 3.3, 1.6 mm)</t>
         </is>
       </c>
       <c r="E552" t="n">
@@ -16685,12 +16685,12 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>p415_FhMTBh4BFxMWGxQOFQ8HAAcd_RICA</t>
+          <t>p417_EgAeBRkGDAAfAQ8BEAACARwW</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>PeriA</t>
+          <t>ICA cav</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -16700,11 +16700,11 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 16.3, 9.9, 6.0, 4.3, 3.4 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 10.7, 8.6, 5.8, 4.8, 2.6, 3.0, 1.8, 1.6 mm)</t>
         </is>
       </c>
       <c r="E553" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -16715,14 +16715,10 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>p414_GgAREAUBFxMNBAUeBwgLFx8Z_LICA</t>
-        </is>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>AComA</t>
-        </is>
-      </c>
+          <t>p420_Bg4cPhUaHgAQDRgAHD4LFxkZ</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr"/>
       <c r="C554" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -16730,11 +16726,11 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 13.8, 10.6, 9.1, 8.0, 4.6, 4.2 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 14.1, 7.4, 6.7, 2.9, 3.1, 2.5, 1.5 mm)</t>
         </is>
       </c>
       <c r="E554" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -16745,12 +16741,12 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>p417_EgAeBRkGDAAfAQ8BEAACARwW</t>
+          <t>p418_HRQVBBwBDBQUAAoGHxQJABkR</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>ICA cav</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -16760,11 +16756,11 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.7, 11.9, 7.2, 5.3, 3.9 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 10.7, 8.1, 5.9, 5.8, 3.3, 2.0, 1.8, 1.7, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E555" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -16775,7 +16771,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>p418_HRQVBBwBDBQUAAoGHxQJABkR</t>
+          <t>p414_GgAREAUBFxMNBAUeBwgLFx8Z_LICA</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -16790,11 +16786,11 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 11.6, 10.3, 7.5, 7.3, 4.5 mm)</t>
+          <t>Saved successfully (cuts: 11 @ 12.9, 8.4, 8.3, 6.4, 3.6, 3.3, 1.8, 1.6, 1.6, 1.6, 1.6 mm)</t>
         </is>
       </c>
       <c r="E556" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -16805,7 +16801,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>p416_FhMTBh4BFxMWGxQOFQ8HAAcd_LICA</t>
+          <t>p403_BAkXCB4cCB8bAA8BBhsaDRAR</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -16820,11 +16816,11 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 14.3, 9.3, 7.8, 7.1, 5.8, 5.2, 4.6 mm)</t>
+          <t>Saved successfully (cuts: 13 @ 13.3, 7.6, 7.0, 6.0, 5.4, 4.6, 4.4, 3.9, 5.7, 2.3, 1.8, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E557" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -16850,11 +16846,11 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 13.8, 11.7, 10.3, 8.3, 5.5, 4.8 mm)</t>
+          <t>Saved successfully (cuts: 11 @ 12.2, 9.5, 8.8, 7.4, 4.9, 3.3, 2.1, 1.8, 1.6, 1.6, 1.6 mm)</t>
         </is>
       </c>
       <c r="E558" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -16865,10 +16861,14 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>p420_Bg4cPhUaHgAQDRgAHD4LFxkZ</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr"/>
+          <t>p423_Eg4HExQBHB8cEBQLGw8MCgAK</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>ICA pcom</t>
+        </is>
+      </c>
       <c r="C559" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -16876,11 +16876,11 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.8, 11.7, 8.3, 4.6, 4.7 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 13.7, 7.8, 5.0, 2.7, 2.6, 2.0, 2.0, 2.0 mm)</t>
         </is>
       </c>
       <c r="E559" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -16891,10 +16891,14 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>p421_FwQADBEGGwQBGwMdHwAADBAK</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr"/>
+          <t>p422_HQ4eDRUaDA4fCQMdHw4CCRAK</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>AComA</t>
+        </is>
+      </c>
       <c r="C560" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -16902,11 +16906,11 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.3, 13.1, 9.3, 8.1, 3.3 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 11.2, 8.1, 7.3, 4.3, 4.0, 4.4, 1.8, 1.5, 1.4 mm)</t>
         </is>
       </c>
       <c r="E560" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -16917,14 +16921,10 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>p422_HQ4eDRUaDA4fCQMdHw4CCRAK</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>AComA</t>
-        </is>
-      </c>
+          <t>p421_FwQADBEGGwQBGwMdHwAADBAK</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr"/>
       <c r="C561" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -16932,11 +16932,11 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.7, 9.5, 8.9, 5.6, 4.4 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 13.0, 7.5, 7.2, 6.0, 3.3, 3.4, 1.9, 1.4 mm)</t>
         </is>
       </c>
       <c r="E561" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -16947,12 +16947,12 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>p423_Eg4HExQBHB8cEBQLGw8MCgAK</t>
+          <t>p424_FBQUDgUaDBQVChMdFhQICgAK</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>MCA M1</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -16962,11 +16962,11 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.0, 9.8, 6.6, 3.8, 3.1 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 13.5, 11.9, 8.1, 5.7, 4.5, 2.6, 2.5 mm)</t>
         </is>
       </c>
       <c r="E562" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -16988,11 +16988,11 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 18.6, 8.0, 7.9, 6.5 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 11.7, 6.8, 6.1, 3.4, 2.1, 3.7, 3.3, 1.7, 1.5, 1.5 mm)</t>
         </is>
       </c>
       <c r="E563" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -17003,12 +17003,12 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>p424_FBQUDgUaDBQVChMdFhQICgAK</t>
+          <t>p429_HBQIGxkWBxsJDAoaCBsHCQAC</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>MCA M1</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -17018,11 +17018,11 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 16.3, 15.2, 9.3, 6.2, 4.7 mm)</t>
+          <t>Saved successfully (cuts: 11 @ 8.5, 5.5, 4.3, 3.7, 3.6, 2.7, 2.7, 1.7, 1.4, 1.4, 1.4 mm)</t>
         </is>
       </c>
       <c r="E564" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -17048,11 +17048,11 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 14.2, 10.1, 10.1, 5.4, 5.0, 4.6, 3.5 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 12.6, 8.9, 8.5, 4.9, 3.9, 3.8, 2.6, 1.8, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E565" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -17063,12 +17063,12 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>p427_FxMXFRUGFxMNFwMbFw8LFxIK</t>
+          <t>p416_FhMTBh4BFxMWGxQOFQ8HAAcd_LICA</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -17078,11 +17078,11 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.9, 11.2, 6.0, 5.0, 3.8 mm)</t>
+          <t>Saved successfully (cuts: 11 @ 11.9, 7.8, 5.7, 5.3, 5.1, 4.5, 2.6, 3.2, 2.4, 2.1, 1.6 mm)</t>
         </is>
       </c>
       <c r="E566" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -17093,12 +17093,12 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>p429_HBQIGxkWBxsJDAoaCBsHCQAC</t>
+          <t>p430_AwAeCA4JHggABAoGAQACDAYZ</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -17108,11 +17108,11 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 19.2, 6.2, 6.1, 6.0, 4.1, 3.7 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 10.6, 10.4, 8.6, 4.6, 4.6, 2.5, 2.2, 2.0 mm)</t>
         </is>
       </c>
       <c r="E567" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>p430_AwAeCA4JHggABAoGAQACDAYZ</t>
+          <t>p427_FxMXFRUGFxMNFwMbFw8LFxIK</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -17138,11 +17138,11 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.3, 11.6, 10.7, 6.6, 6.3 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 12.2, 6.7, 4.9, 3.1, 2.7, 3.4, 3.0, 1.6, 1.6, 1.6 mm)</t>
         </is>
       </c>
       <c r="E568" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -17153,10 +17153,14 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>p431_BBIbFR8bDBIaEQkcBhIHERoL</t>
-        </is>
-      </c>
-      <c r="B569" t="inlineStr"/>
+          <t>p432_BgQcBAQSDAQdABIVBAQAAAEC</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>AComA</t>
+        </is>
+      </c>
       <c r="C569" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -17164,11 +17168,11 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 14.6, 10.6, 6.2, 5.7, 4.2, 4.1, 4.0 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 12.7, 10.9, 6.2, 6.0, 5.7, 4.9, 2.5, 1.9, 1.8 mm)</t>
         </is>
       </c>
       <c r="E569" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -17179,7 +17183,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>p432_BgQcBAQSDAQdABIVBAQAAAEC</t>
+          <t>p435_FAQeCAQaHRsNAAoGBhMBHxEd</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -17194,11 +17198,11 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 22.5, 13.0, 7.5, 7.2, 6.9, 3.7 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 14.9, 9.9, 7.7, 6.6, 4.5, 1.9, 1.6 mm)</t>
         </is>
       </c>
       <c r="E570" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -17220,11 +17224,11 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.1, 12.1, 9.8, 7.9, 5.2 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 12.8, 10.5, 8.4, 6.5, 4.8, 2.2, 1.9, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E571" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -17250,11 +17254,11 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 11.1, 10.3, 5.3, 3.5 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 10.0, 8.6, 4.7, 3.2, 1.9, 1.9 mm)</t>
         </is>
       </c>
       <c r="E572" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -17265,14 +17269,10 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>p435_FAQeCAQaHRsNAAoGBhMBHxEd</t>
-        </is>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>AComA</t>
-        </is>
-      </c>
+          <t>p431_BBIbFR8bDBIaEQkcBhIHERoL</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr"/>
       <c r="C573" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -17280,11 +17280,11 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 16.3, 15.1, 13.2, 9.1, 6.8 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 12.8, 5.9, 4.8, 3.7, 3.6, 3.4, 3.1, 2.0, 1.8, 1.5 mm)</t>
         </is>
       </c>
       <c r="E573" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -17306,11 +17306,11 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 15.8, 13.1, 10.5, 9.4, 8.8, 7.4, 5.7 mm)</t>
+          <t>Saved successfully (cuts: 12 @ 14.3, 10.6, 9.2, 8.1, 7.3, 5.0, 4.4, 2.4, 2.2, 1.9, 1.6, 1.6 mm)</t>
         </is>
       </c>
       <c r="E574" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -17321,14 +17321,10 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>p437_FAQQDh4bDAQRCggcFgQMChsL</t>
-        </is>
-      </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t>MCA bif</t>
-        </is>
-      </c>
+          <t>p446_Ag4WExkPBwQJGwkLAAgJEBAC_RICA</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr"/>
       <c r="C575" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -17336,11 +17332,11 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 19.8, 11.3, 8.7, 7.5, 6.6, 3.7 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 9.4, 8.8, 5.2, 4.1, 2.7, 2.0, 1.7, 1.4 mm)</t>
         </is>
       </c>
       <c r="E575" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -17351,10 +17347,14 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>p438_AggQAAUQDAgRBBMXAAgMBAAA</t>
-        </is>
-      </c>
-      <c r="B576" t="inlineStr"/>
+          <t>p449_AxUHAhsRDBUGBg0WARUbBh4B</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>ICA pcom</t>
+        </is>
+      </c>
       <c r="C576" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -17362,11 +17362,11 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 11.5, 10.2, 9.6, 5.6, 4.6 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 20.4, 10.9, 7.3, 6.9, 6.1, 2.1, 2.0 mm)</t>
         </is>
       </c>
       <c r="E576" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>p439_HwYbBAIWFQgWFwkIGwQcChIR_RICA</t>
+          <t>p441_AgQHEhUWFxQAABQKBxILFxAN</t>
         </is>
       </c>
       <c r="B577" t="inlineStr"/>
@@ -17388,11 +17388,11 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 14.5, 12.7, 11.6, 4.7 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.1, 9.5, 6.5, 5.6, 4.2, 3.8, 2.0, 1.7 mm)</t>
         </is>
       </c>
       <c r="E577" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -17403,14 +17403,10 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>p440_HwYbBAIWFQgWFwkIGwQcChIR_LICA</t>
-        </is>
-      </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>ICA chor</t>
-        </is>
-      </c>
+          <t>p443_FQgRCRUGEAQBAgMdDAgNDRAW</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr"/>
       <c r="C578" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -17418,11 +17414,11 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.3, 12.7, 9.1, 5.2, 3.2 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 14.6, 6.1, 6.0, 3.6, 2.8, 2.9, 2.6, 2.0, 1.8 mm)</t>
         </is>
       </c>
       <c r="E578" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -17433,7 +17429,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>p441_AgQHEhUWFxQAABQKBxILFxAN</t>
+          <t>p438_AggQAAUQDAgRBBMXAAgMBAAA</t>
         </is>
       </c>
       <c r="B579" t="inlineStr"/>
@@ -17444,11 +17440,11 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 13.5, 10.5, 8.3, 8.2, 5.5, 5.0 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 10.6, 9.0, 7.9, 3.7, 3.0, 2.0, 1.5, 1.5 mm)</t>
         </is>
       </c>
       <c r="E579" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -17459,7 +17455,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>p443_FQgRCRUGEAQBAgMdDAgNDRAW</t>
+          <t>p439_HwYbBAIWFQgWFwkIGwQcChIR_RICA</t>
         </is>
       </c>
       <c r="B580" t="inlineStr"/>
@@ -17470,11 +17466,11 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 16.1, 8.5, 8.1, 7.0, 4.5 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.9, 11.0, 9.7, 4.2, 2.4, 2.3, 2.2, 1.6 mm)</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -17485,12 +17481,12 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>p442_EhMHDx4NAB8BEAgBFxMMFwAW_RICA</t>
+          <t>p440_HwYbBAIWFQgWFwkIGwQcChIR_LICA</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>MCA M1</t>
+          <t>ICA chor</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -17500,11 +17496,11 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 12.9, 10.9, 9.5, 6.4, 5.4, 5.2, 5.0 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 11.8, 9.4, 7.2, 4.9, 3.0, 2.4, 2.1, 1.9 mm)</t>
         </is>
       </c>
       <c r="E581" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -17515,10 +17511,14 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>p444_GBQVFBUGHRUHABgaFRQLCxoM</t>
-        </is>
-      </c>
-      <c r="B582" t="inlineStr"/>
+          <t>p437_FAQQDh4bDAQRCggcFgQMChsL</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>MCA bif</t>
+        </is>
+      </c>
       <c r="C582" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -17526,11 +17526,11 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.6, 10.8, 8.1, 8.0, 6.0, 4.2 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 16.9, 5.8, 5.7, 5.7, 4.4, 3.5, 4.8, 3.1, 2.0, 1.8 mm)</t>
         </is>
       </c>
       <c r="E582" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -17541,10 +17541,14 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>p446_Ag4WExkPBwQJGwkLAAgJEBAC_RICA</t>
-        </is>
-      </c>
-      <c r="B583" t="inlineStr"/>
+          <t>p450_FAQtDhwBBAQaFwcRFz4BCRwO</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>AComA</t>
+        </is>
+      </c>
       <c r="C583" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -17552,11 +17556,11 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 11.5, 10.0, 7.9, 4.0 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 14.6, 11.4, 10.8, 10.2, 5.4, 4.8, 2.6 mm)</t>
         </is>
       </c>
       <c r="E583" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -17567,7 +17571,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>p447_GBQfAxUaBh8GCAQKABUGEBga</t>
+          <t>p454_BwQeDRkGFQQBGwMDHggAAhAK</t>
         </is>
       </c>
       <c r="B584" t="inlineStr"/>
@@ -17578,11 +17582,11 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 17.5, 8.0, 6.8, 3.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 11.1, 10.3, 7.8, 5.4, 5.0, 3.3, 1.7, 1.6 mm)</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -17604,11 +17608,11 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 18.9, 12.5, 11.3, 8.3, 6.5 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 12.9, 11.6, 10.0, 7.5, 6.0, 2.1, 5.1 mm)</t>
         </is>
       </c>
       <c r="E585" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -17619,12 +17623,12 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>p449_AxUHAhsRDBUGBg0WARUbBh4B</t>
+          <t>p442_EhMHDx4NAB8BEAgBFxMMFwAW_RICA</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>MCA M1</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -17634,11 +17638,11 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 26.4, 12.6, 10.0, 9.3 mm)</t>
+          <t>Saved successfully (cuts: 11 @ 11.7, 9.8, 4.9, 4.9, 4.6, 4.4, 3.0, 5.3, 1.8, 1.8, 1.6 mm)</t>
         </is>
       </c>
       <c r="E586" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -17649,12 +17653,12 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>p450_FAQtDhwBBAQaFwcRFz4BCRwO</t>
+          <t>p457_BA4ADxERDA4BCwcWBg4cCxQB</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -17664,7 +17668,7 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 15.5, 12.5, 12.4, 12.3, 6.6, 6.3, 3.4 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 12.0, 8.8, 6.4, 6.3, 6.2, 1.8, 1.8 mm)</t>
         </is>
       </c>
       <c r="E587" t="n">
@@ -17679,10 +17683,14 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>p451_FwQADBEGGwQBGwMdHwAADBAK_LICA</t>
-        </is>
-      </c>
-      <c r="B588" t="inlineStr"/>
+          <t>p453_FAQQDh4GFxcaCQoKDAQMChsW</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>ICA bif</t>
+        </is>
+      </c>
       <c r="C588" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -17690,11 +17698,11 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 14.8, 12.3, 8.7, 7.2, 7.0, 4.7, 4.6 mm)</t>
+          <t>Saved successfully (cuts: 12 @ 11.4, 10.5, 7.9, 5.1, 4.1, 3.7, 3.3, 2.2, 2.1, 1.9, 1.7, 1.6 mm)</t>
         </is>
       </c>
       <c r="E588" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -17705,14 +17713,10 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>p453_FAQQDh4GFxcaCQoKDAQMChsW</t>
-        </is>
-      </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>ICA bif</t>
-        </is>
-      </c>
+          <t>p455_HQAACB8cBggNBBQGHRUaDBgZ</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr"/>
       <c r="C589" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -17720,11 +17724,11 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.8, 11.7, 11.1, 7.0, 6.7, 4.5 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.5, 8.2, 7.0, 3.9, 2.9, 5.1, 2.2, 1.5 mm)</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -17735,7 +17739,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>p456_BhQbDRwNDBQaCQoKBBQHCRkd</t>
+          <t>p444_GBQVFBUGHRUHABgaFRQLCxoM</t>
         </is>
       </c>
       <c r="B590" t="inlineStr"/>
@@ -17746,11 +17750,11 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 11.0, 10.5, 9.6, 7.0, 4.4, 3.3 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 11.9, 8.3, 7.5, 6.2, 4.0, 3.4, 2.2, 2.7, 1.6 mm)</t>
         </is>
       </c>
       <c r="E590" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -17761,7 +17765,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>p452_EQITDAAHAAANBgcCAg4cBBQb</t>
+          <t>p451_FwQADBEGGwQBGwMdHwAADBAK_LICA</t>
         </is>
       </c>
       <c r="B591" t="inlineStr"/>
@@ -17772,11 +17776,11 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 15.2, 10.6, 9.6, 9.0, 7.9, 7.5, 5.0 mm)</t>
+          <t>Saved successfully (cuts: 12 @ 11.5, 6.9, 5.8, 5.5, 4.0, 3.8, 3.7, 2.6, 2.2, 1.9, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -17787,7 +17791,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>p455_HQAACB8cBggNBBQGHRUaDBgZ</t>
+          <t>p452_EQITDAAHAAANBgcCAg4cBBQb</t>
         </is>
       </c>
       <c r="B592" t="inlineStr"/>
@@ -17798,11 +17802,11 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 15.8, 8.7, 3.9, 3.7 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 14.1, 9.1, 7.7, 7.5, 6.0, 4.5, 4.1, 3.0, 1.8, 1.7 mm)</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -17813,10 +17817,14 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>p454_BwQeDRkGFQQBGwMDHggAAhAK</t>
-        </is>
-      </c>
-      <c r="B593" t="inlineStr"/>
+          <t>p461_AgAECBUaDAAFDAMdAAAYDBAK</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>PeriA</t>
+        </is>
+      </c>
       <c r="C593" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -17824,11 +17832,11 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.2, 11.9, 8.9, 7.4, 5.3, 3.8 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 11.5, 8.7, 6.7, 5.2, 5.0, 2.7, 1.6 mm)</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -17839,12 +17847,12 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>p458_HQ4cDxUcDA4dCwMbHw4ACxAM</t>
+          <t>p459_FBQRExUcDBQQFwMbFhQNFxAM</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -17854,7 +17862,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 9 @ 14.9, 10.8, 9.4, 6.5, 6.0, 5.8, 5.6, 4.8, 4.1 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 13.2, 9.1, 8.5, 8.4, 8.0, 5.8, 1.7, 1.7, 1.6 mm)</t>
         </is>
       </c>
       <c r="E594" t="n">
@@ -17869,12 +17877,12 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>p457_BA4ADxERDA4BCwcWBg4cCxQB</t>
+          <t>p460_CgQcBhUaDAQdAgMdCAQAAhAK</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -17884,11 +17892,11 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.5, 10.4, 7.5, 7.1, 6.8 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 11.6, 9.7, 6.8, 5.2, 2.3, 1.9, 1.7 mm)</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -17899,12 +17907,12 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>p459_FBQRExUcDBQQFwMbFhQNFxAM</t>
+          <t>p462_EwAADxURDAABCwMWEQAcCxAB</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>MCA M1</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -17914,11 +17922,11 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 15.8, 10.1, 9.9, 9.3, 9.0, 6.4 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 11.2, 8.3, 6.7, 3.3, 2.9, 2.7, 2.6 mm)</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -17929,14 +17937,10 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>p461_AgAECBUaDAAFDAMdAAAYDBAK</t>
-        </is>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>PeriA</t>
-        </is>
-      </c>
+          <t>p447_GBQfAxUaBh8GCAQKABUGEBga</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr"/>
       <c r="C597" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -17944,11 +17948,11 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.5, 9.7, 6.9, 6.3, 6.0 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 15.0, 6.8, 4.3, 2.4, 1.9, 1.6 mm)</t>
         </is>
       </c>
       <c r="E597" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -17959,14 +17963,10 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>p460_CgQcBhUaDAQdAgMdCAQAAhAK</t>
-        </is>
-      </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>ICA oph</t>
-        </is>
-      </c>
+          <t>p456_BhQbDRwNDBQaCQoKBBQHCRkd</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr"/>
       <c r="C598" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -17974,11 +17974,11 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 13.8, 13.1, 8.5, 7.0 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 10.4, 8.1, 7.6, 5.0, 3.3, 1.7, 1.6, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E598" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -17989,12 +17989,12 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>p462_EwAADxURDAABCwMWEQAcCxAB</t>
+          <t>p458_HQ4cDxUcDA4dCwMbHw4ACxAM</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>MCA M1</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -18004,11 +18004,11 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.1, 9.7, 8.3, 4.8, 3.8 mm)</t>
+          <t>Saved successfully (cuts: 13 @ 14.0, 9.4, 7.5, 6.1, 5.4, 5.3, 5.1, 4.4, 3.6, 1.9, 1.6, 1.5, 1.5 mm)</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -18019,10 +18019,14 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>p463_AwAQCB8WEwMaChUOEAgBFhQa</t>
-        </is>
-      </c>
-      <c r="B600" t="inlineStr"/>
+          <t>p464_ARQABAMAGx8GFwMcGggfEAcd</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>AComA</t>
+        </is>
+      </c>
       <c r="C600" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18030,11 +18034,11 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 15.5, 12.8, 11.4, 10.0, 8.1, 6.7, 5.7 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 12.6, 11.2, 8.2, 7.6, 7.4, 2.4 mm)</t>
         </is>
       </c>
       <c r="E600" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -18060,11 +18064,11 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.5, 13.0, 11.8, 8.5, 7.1 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 13.6, 10.3, 9.8, 6.8, 4.6, 3.7, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -18075,12 +18079,12 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>p464_ARQABAMAGx8GFwMcGggfEAcd</t>
+          <t>p468_BgQAAAMcFwYGDBgKAAAdERAf</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -18090,11 +18094,11 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.5, 12.9, 9.4, 9.2, 8.6 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 11.8, 10.8, 7.1, 3.1, 2.0, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E602" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -18105,14 +18109,10 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>p465_Ag4BBAINHBINChUKAAQAFgcX</t>
-        </is>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>AComA</t>
-        </is>
-      </c>
+          <t>p463_AwAQCB8WEwMaChUOEAgBFhQa</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr"/>
       <c r="C603" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18120,11 +18120,11 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.5, 10.7, 10.5, 9.8, 3.2 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 14.2, 12.1, 9.2, 9.2, 6.6, 6.0, 4.4, 2.1, 1.8, 1.5 mm)</t>
         </is>
       </c>
       <c r="E603" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -18135,12 +18135,12 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>p468_BgQAAAMcFwYGDBgKAAAdERAf</t>
+          <t>p465_Ag4BBAINHBINChUKAAQAFgcX</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -18150,11 +18150,11 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.8, 12.0, 8.1, 4.2, 7.0 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 13.6, 9.6, 9.3, 8.3, 2.9, 2.8, 1.4, 1.4 mm)</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>p467_Bg4HFRESDA4GEQcVBA4bERQC</t>
+          <t>p471_EhMXEhMBEx8BABUMGwAMFxAL</t>
         </is>
       </c>
       <c r="B605" t="inlineStr"/>
@@ -18176,11 +18176,11 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 11.0, 10.4, 9.6, 6.2, 5.0, 4.9 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 16.1, 9.7, 9.1, 6.1, 6.0, 1.9, 1.8, 1.7 mm)</t>
         </is>
       </c>
       <c r="E605" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -18191,10 +18191,14 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>p469_EQ8WExURDA8XFwMWEw8KFxAB</t>
-        </is>
-      </c>
-      <c r="B606" t="inlineStr"/>
+          <t>p470_Gw4EABMNBAgQGwkZEwILExwb</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>ICA cav</t>
+        </is>
+      </c>
       <c r="C606" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18202,11 +18206,11 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.5, 11.4, 10.4, 9.6, 7.9, 6.1 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 10.7, 9.5, 8.0, 6.5, 1.9, 1.5, 1.5 mm)</t>
         </is>
       </c>
       <c r="E606" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -18217,12 +18221,12 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>p470_Gw4EABMNBAgQGwkZEwILExwb</t>
+          <t>p474_FAgdFBYWGw4GAwIGHRQIARwX_RICA</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>ICA cav</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -18232,11 +18236,11 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 11.8, 11.7, 10.0, 6.8, 4.1 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 10.1, 8.3, 7.3, 6.1, 5.8, 3.5 mm)</t>
         </is>
       </c>
       <c r="E607" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -18247,7 +18251,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>p471_EhMXEhMBEx8BABUMGwAMFxAL</t>
+          <t>p473_AxQRCRUcDBQQDQMbARQNDRAM</t>
         </is>
       </c>
       <c r="B608" t="inlineStr"/>
@@ -18258,11 +18262,11 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 17.2, 11.2, 9.6, 7.9, 7.7 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 10.8, 10.3, 9.3, 8.4, 8.3, 2.2, 1.7, 1.7, 1.6 mm)</t>
         </is>
       </c>
       <c r="E608" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -18273,14 +18277,10 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>p472_HAAACAYBFxMWGwcdGxcHAAcd</t>
-        </is>
-      </c>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>ICA pcom</t>
-        </is>
-      </c>
+          <t>p467_Bg4HFRESDA4GEQcVBA4bERQC</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr"/>
       <c r="C609" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18288,11 +18288,11 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 14.8, 13.9, 12.3, 9.6, 8.8, 3.7 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 9.5, 9.5, 8.4, 5.5, 5.0, 4.1, 1.9, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E609" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -18303,12 +18303,12 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>p474_FAgdFBYWGw4GAwIGHRQIARwX_RICA</t>
+          <t>p480_GRIXDxkWAQQdDA8cFw8HDAYd_LICA</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -18318,11 +18318,11 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.7, 10.3, 7.5, 7.1, 5.9 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 15.1, 11.3, 7.8, 4.3, 2.3, 1.5 mm)</t>
         </is>
       </c>
       <c r="E610" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -18333,10 +18333,14 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>p473_AxQRCRUcDBQQDQMbARQNDRAM</t>
-        </is>
-      </c>
-      <c r="B611" t="inlineStr"/>
+          <t>p476_Ag4RCREcDA4QDQcbAA4NDRQM</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>AComA</t>
+        </is>
+      </c>
       <c r="C611" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18344,11 +18348,11 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.8, 11.2, 10.6, 10.2, 9.9 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 12.4, 11.3, 9.1, 8.5, 8.3, 3.9, 6.5, 2.2, 1.8, 1.5 mm)</t>
         </is>
       </c>
       <c r="E611" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -18370,11 +18374,11 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.9, 11.7, 10.1, 5.9, 4.9 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 10.6, 10.6, 8.0, 6.0, 4.7, 2.3, 1.9, 1.5 mm)</t>
         </is>
       </c>
       <c r="E612" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -18385,12 +18389,12 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>p478_FhMdEgMJAAUNFwkcAQAcARMK</t>
+          <t>p477_EgAIDgYNABMKGwcVHRcLFwcB</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>ICA bif</t>
+          <t>ICA cav</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -18400,11 +18404,11 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 15.2, 14.2, 13.5, 7.7 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 13.1, 9.4, 7.4, 5.9, 5.7, 5.3, 1.8 mm)</t>
         </is>
       </c>
       <c r="E613" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -18415,12 +18419,12 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>p477_EgAIDgYNABMKGwcVHRcLFwcB</t>
+          <t>p478_FhMdEgMJAAUNFwkcAQAcARMK</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>ICA cav</t>
+          <t>ICA bif</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -18430,11 +18434,11 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 17.4, 10.1, 9.7, 7.4, 6.2 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 13.4, 10.9, 10.4, 5.3, 4.1, 2.6, 2.4 mm)</t>
         </is>
       </c>
       <c r="E614" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -18445,7 +18449,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>p476_Ag4RCREcDA4QDQcbAA4NDRQM</t>
+          <t>p479_FBMdGw4aHRsXFwkVFhMBHxEK</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -18460,7 +18464,7 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 15.7, 12.1, 11.1, 10.6, 9.5, 4.7, 4.7 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 11.0, 8.8, 7.6, 6.1, 5.4, 1.9, 1.7 mm)</t>
         </is>
       </c>
       <c r="E615" t="n">
@@ -18475,12 +18479,12 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>p479_FBMdGw4aHRsXFwkVFhMBHxEK</t>
+          <t>p472_HAAACAYBFxMWGwcdGxcHAAcd</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -18490,11 +18494,11 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.3, 9.4, 8.7, 7.7, 5.8 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 13.1, 11.5, 11.1, 8.8, 8.3, 2.4, 2.1, 1.9, 1.6 mm)</t>
         </is>
       </c>
       <c r="E616" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -18505,14 +18509,10 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>p480_GRIXDxkWAQQdDA8cFw8HDAYd_LICA</t>
-        </is>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>ICA pcom</t>
-        </is>
-      </c>
+          <t>p469_EQ8WExURDA8XFwMWEw8KFxAB</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr"/>
       <c r="C617" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18520,11 +18520,11 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 16.6, 12.6, 8.4, 4.7 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 11.4, 10.4, 9.0, 8.6, 7.7, 5.1, 1.9, 1.8, 1.5, 1.4 mm)</t>
         </is>
       </c>
       <c r="E617" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -18535,12 +18535,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>p481_GRIXDxkWAQQdDA8cFw8HDAYd_RICA</t>
+          <t>p484_FwgADhQWGxMcAQEGAA4KAhwK</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -18550,11 +18550,11 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 18.1, 14.2, 11.4, 7.5, 4.2 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 16.7, 11.2, 10.8, 8.9, 6.3, 3.7, 3.2 mm)</t>
         </is>
       </c>
       <c r="E618" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -18565,40 +18565,40 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>p482_AwAaCAQBDAAbDBIGAQAGDAER</t>
-        </is>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>AComA</t>
-        </is>
-      </c>
+          <t>p483_CQABEhkGDAAAFg8BCwAdFhwW</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr"/>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Skipped</t>
+          <t>Saved</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>Error: 'UnstructuredGrid' object has no attribute 'is_all_triangles'</t>
+          <t>Saved successfully (cuts: 4 @ 14.2, 10.0, 9.3, 5.0 mm)</t>
         </is>
       </c>
       <c r="E619" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>p483_CQABEhkGDAAAFg8BCwAdFhwW</t>
-        </is>
-      </c>
-      <c r="B620" t="inlineStr"/>
+          <t>p481_GRIXDxkWAQQdDA8cFw8HDAYd_RICA</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>ICA pcom</t>
+        </is>
+      </c>
       <c r="C620" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18606,11 +18606,11 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 14.8, 12.5, 11.1, 5.4 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 15.5, 13.8, 10.0, 6.1, 3.7, 2.9, 1.7, 1.6 mm)</t>
         </is>
       </c>
       <c r="E620" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -18621,12 +18621,12 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>p484_FwgADhQWGxMcAQEGAA4KAhwK</t>
+          <t>p487_BwAVBB4WEwYWCxEOFQQAEhQf</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>PeriA</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -18636,11 +18636,11 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 20.8, 14.9, 13.6, 9.8, 6.8, 4.4, 3.1 mm)</t>
+          <t>Saved successfully (cuts: 11 @ 10.0, 6.1, 6.1, 4.4, 4.0, 3.9, 3.7, 2.0, 1.9, 1.5, 1.4 mm)</t>
         </is>
       </c>
       <c r="E621" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -18651,12 +18651,12 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>p485_FwkXAwINHAQUEBURGgQMFxAW</t>
+          <t>p482_AwAaCAQBDAAbDBIGAQAGDAER</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -18666,11 +18666,11 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 13.6, 8.9, 8.6, 8.3, 6.5, 5.2 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 13.4, 12.8, 11.7, 10.2, 7.0, 2.6, 2.1, 1.9 mm)</t>
         </is>
       </c>
       <c r="E622" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -18681,12 +18681,12 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>p486_AwQAFxEBAR8WFxAOGxIdAAcO</t>
+          <t>p488_BAkbBAIRDAkaABQWBgkHAAcB_LV</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>PICA</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -18696,11 +18696,11 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.6, 12.3, 10.5, 9.3, 5.7 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 14.5, 11.7, 11.3, 9.9, 7.4, 1.9, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E623" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -18711,14 +18711,10 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>p487_BwAVBB4WEwYWCxEOFQQAEhQf</t>
-        </is>
-      </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>PeriA</t>
-        </is>
-      </c>
+          <t>p493_AgQbEi8aGwMWDBQADAQHFioK</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr"/>
       <c r="C624" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18726,11 +18722,11 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 11.2, 8.1, 6.7, 5.4, 5.2, 4.9, 4.2 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 23.8, 15.1, 11.8, 9.1, 7.6, 1.8 mm)</t>
         </is>
       </c>
       <c r="E624" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -18741,12 +18737,12 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>p488_BAkbBAIRDAkaABQWBgkHAAcB_LV</t>
+          <t>p489_BAkbBAIRDAkaABQWBgkHAAcB_LICA</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>PICA</t>
+          <t>ICA chor</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -18756,11 +18752,11 @@
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 15.9, 12.6, 11.4, 10.5, 8.2, 6.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 13.3, 10.3, 8.8, 7.8, 5.5, 2.4, 2.4, 1.4 mm)</t>
         </is>
       </c>
       <c r="E625" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -18771,12 +18767,12 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>p489_BAkbBAIRDAkaABQWBgkHAAcB_LICA</t>
+          <t>p496_HQgeCRkcDAgfDQ8bHwgCDRwM</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>ICA chor</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -18786,11 +18782,11 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.9, 11.9, 10.7, 8.0, 6.7 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 15.0, 13.4, 13.1, 9.2, 9.0, 1.4 mm)</t>
         </is>
       </c>
       <c r="E626" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -18801,7 +18797,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>p493_AgQbEi8aGwMWDBQADAQHFioK</t>
+          <t>p494_FwARCR8dFh8SBg4ABwUJBBYQ</t>
         </is>
       </c>
       <c r="B627" t="inlineStr"/>
@@ -18812,11 +18808,11 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 26.6, 16.0, 14.2, 9.3, 8.4, 4.2 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 14.0, 12.4, 9.1, 8.5, 2.3 mm)</t>
         </is>
       </c>
       <c r="E627" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -18827,10 +18823,14 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>p490_EhMHDx4NAB8BEAgBFxMMFwAW</t>
-        </is>
-      </c>
-      <c r="B628" t="inlineStr"/>
+          <t>p492_EgQcFxUGBxUaGwMBBAQAEAER_LICA</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>ICA cav</t>
+        </is>
+      </c>
       <c r="C628" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18838,11 +18838,11 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 8 @ 13.6, 12.4, 11.4, 10.0, 8.6, 7.5, 6.9, 5.5 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 12.5, 11.1, 10.8, 8.9, 6.1, 2.3 mm)</t>
         </is>
       </c>
       <c r="E628" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -18853,14 +18853,10 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>p492_EgQcFxUGBxUaGwMBBAQAEAER_LICA</t>
-        </is>
-      </c>
-      <c r="B629" t="inlineStr">
-        <is>
-          <t>ICA cav</t>
-        </is>
-      </c>
+          <t>p491_EgQcFxUGBxUaGwMBBAQAEAER_RICA</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr"/>
       <c r="C629" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18868,11 +18864,11 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.2, 12.2, 12.2, 10.3, 6.7 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.7, 8.8, 8.4, 4.2, 4.0, 4.9, 1.8, 1.4 mm)</t>
         </is>
       </c>
       <c r="E629" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -18883,10 +18879,14 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>p491_EgQcFxUGBxUaGwMBBAQAEAER_RICA</t>
-        </is>
-      </c>
-      <c r="B630" t="inlineStr"/>
+          <t>p486_AwQAFxEBAR8WFxAOGxIdAAcO</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>MCA bif</t>
+        </is>
+      </c>
       <c r="C630" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18894,11 +18894,11 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 17.1, 9.3, 8.7, 5.1, 5.0 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.2, 11.3, 8.5, 8.3, 3.9, 2.2, 1.8, 1.5 mm)</t>
         </is>
       </c>
       <c r="E630" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -18909,10 +18909,14 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>p494_FwARCR8dFh8SBg4ABwUJBBYQ</t>
-        </is>
-      </c>
-      <c r="B631" t="inlineStr"/>
+          <t>p485_FwkXAwINHAQUEBURGgQMFxAW</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>MCA bif</t>
+        </is>
+      </c>
       <c r="C631" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18920,11 +18924,11 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 15.4, 13.3, 11.6, 9.7 mm)</t>
+          <t>Saved successfully (cuts: 12 @ 10.8, 7.7, 7.5, 6.8, 5.1, 3.4, 2.3, 2.2, 1.9, 1.6, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E631" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -18935,10 +18939,14 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>p495_AAQAExkGDAQBFw8BAgQcFxwW</t>
-        </is>
-      </c>
-      <c r="B632" t="inlineStr"/>
+          <t>p497_AwIaCBUbAR8QDQ8KARIdBh0R</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>MCA bif</t>
+        </is>
+      </c>
       <c r="C632" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -18946,11 +18954,11 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 13.8, 12.9, 9.2, 8.5, 8.4, 7.8, 5.0 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.7, 10.7, 10.1, 8.8, 7.3, 3.4, 2.3, 1.8 mm)</t>
         </is>
       </c>
       <c r="E632" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -18961,12 +18969,12 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>p496_HQgeCRkcDAgfDQ8bHwgCDRwM</t>
+          <t>p504_Gw4dHx8HGQ4cDgkAGQ4BDhoX</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>ICA cav</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -18976,7 +18984,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.4, 14.1, 13.6, 10.5, 9.6 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 13.3, 11.8, 9.3, 2.0, 1.4 mm)</t>
         </is>
       </c>
       <c r="E633" t="n">
@@ -18991,12 +18999,12 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>p498_Fw4fBAoWHQwWHwEAHwQUAhoV_LICA</t>
+          <t>p502_Ag4LHx8RAA4KFwkWAA4XFxoB_RICA</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>MCA M1</t>
+          <t>PeriA</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -19006,11 +19014,11 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 12.2, 11.4, 10.8, 9.7, 6.1 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 13.9, 7.9, 5.6, 3.9, 3.6, 3.0, 1.9, 1.5, 1.5 mm)</t>
         </is>
       </c>
       <c r="E634" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -19021,14 +19029,10 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>p497_AwIaCBUbAR8QDQ8KARIdBh0R</t>
-        </is>
-      </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>MCA bif</t>
-        </is>
-      </c>
+          <t>p499_Fw4fBAoWHQwWHwEAHwQUAhoV_RICA</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr"/>
       <c r="C635" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19036,11 +19040,11 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 17.5, 13.0, 11.3, 11.0, 7.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 11.7, 11.3, 9.4, 8.8, 6.8, 4.9, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E635" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -19051,14 +19055,10 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>p500_FAAtEhkEBAANBDkcGw0YBBEZ</t>
-        </is>
-      </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>MCA bif</t>
-        </is>
-      </c>
+          <t>p490_EhMHDx4NAB8BEAgBFxMMFwAW</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr"/>
       <c r="C636" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19066,11 +19066,11 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.3, 11.5, 10.8, 10.2, 8.0, 6.2 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 12.4, 10.3, 9.8, 9.6, 8.0, 6.9, 6.2, 5.1, 2.3, 1.8 mm)</t>
         </is>
       </c>
       <c r="E636" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -19081,10 +19081,14 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>p499_Fw4fBAoWHQwWHwEAHwQUAhoV_RICA</t>
-        </is>
-      </c>
-      <c r="B637" t="inlineStr"/>
+          <t>p498_Fw4fBAoWHQwWHwEAHwQUAhoV_LICA</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>MCA M1</t>
+        </is>
+      </c>
       <c r="C637" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19092,11 +19096,11 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 13.6, 11.5, 10.9, 9.7, 7.8, 6.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 11.2, 9.7, 9.1, 8.2, 3.4, 2.0, 1.9, 1.7 mm)</t>
         </is>
       </c>
       <c r="E637" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -19107,12 +19111,12 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>p502_Ag4LHx8RAA4KFwkWAA4XFxoB_RICA</t>
+          <t>p510_EhMdAhgBFxMNFwkMGggLFxcK_RV</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>PeriA</t>
+          <t>PICA</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -19122,7 +19126,7 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.7, 12.3, 6.6, 6.4, 4.9 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 11.8, 10.9, 9.3, 1.9, 1.5 mm)</t>
         </is>
       </c>
       <c r="E638" t="n">
@@ -19152,11 +19156,11 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 13.6, 9.7, 9.7, 9.2, 4.9 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.4, 9.0, 8.4, 8.1, 4.2, 1.9, 1.8, 1.7 mm)</t>
         </is>
       </c>
       <c r="E639" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -19167,12 +19171,12 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>p504_Gw4dHx8HGQ4cDgkAGQ4BDhoX</t>
+          <t>p503_Ag4LHx8RAA4KFwkWAA4XFxoB_LICA</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>ICA cav</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -19182,11 +19186,11 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 14.3, 13.5, 9.8, 5.3 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 11.6, 11.3, 9.9, 9.0, 7.7, 5.6, 2.8, 1.6 mm)</t>
         </is>
       </c>
       <c r="E640" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -19197,12 +19201,12 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>p503_Ag4LHx8RAA4KFwkWAA4XFxoB_LICA</t>
+          <t>p509_EhMdAhgBFxMNFwkMGggLFxcK_RICA</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -19212,7 +19216,7 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 13.1, 12.3, 10.7, 9.5, 9.4, 8.6 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 20.9, 15.5, 14.8, 13.4, 2.8, 2.0 mm)</t>
         </is>
       </c>
       <c r="E641" t="n">
@@ -19242,11 +19246,11 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.0, 12.8, 12.5, 8.9, 5.0 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 14.1, 11.7, 10.8, 8.8, 5.0, 2.2 mm)</t>
         </is>
       </c>
       <c r="E642" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -19257,12 +19261,12 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>p506_BgAeAhUbEQkaCw8REw0NAAYb</t>
+          <t>p513_BA4MDgQHBg4HChIABg4aCgEX</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -19272,11 +19276,11 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.4, 14.5, 11.1, 8.8, 4.7 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 14.4, 8.5, 8.2, 7.1, 2.2, 2.0, 1.5 mm)</t>
         </is>
       </c>
       <c r="E643" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -19287,12 +19291,12 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>p505_FwQAAxEdHhUNABQNExQCERId</t>
+          <t>p500_FAAtEhkEBAANBDkcGw0YBBEZ</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -19302,11 +19306,11 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 16.9, 16.3, 15.5, 15.5, 14.9, 8.8 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 11.2, 10.3, 9.5, 6.8, 5.9, 5.6, 1.6, 1.5, 1.4 mm)</t>
         </is>
       </c>
       <c r="E644" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -19317,12 +19321,12 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>p510_EhMdAhgBFxMNFwkMGggLFxcK_RV</t>
+          <t>p506_BgAeAhUbEQkaCw8REw0NAAYb</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>PICA</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -19332,11 +19336,11 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 3 @ 13.5, 11.6, 9.4 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 13.8, 11.8, 10.4, 7.6, 4.0, 3.6, 1.8, 1.8, 1.4 mm)</t>
         </is>
       </c>
       <c r="E645" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -19347,10 +19351,14 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>p508_BAQfERUEDAQeFQMDBgQDFRAU_LICA</t>
-        </is>
-      </c>
-      <c r="B646" t="inlineStr"/>
+          <t>p527_Eg4ADxEGFh8cFwgOHAUMCgcW</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>PCA P1-P2</t>
+        </is>
+      </c>
       <c r="C646" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19358,11 +19366,11 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 17.1, 16.2, 14.6, 14.5, 12.5, 12.2, 11.2 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 8.9, 8.2, 7.5, 2.6, 2.0, 1.5 mm)</t>
         </is>
       </c>
       <c r="E646" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -19373,14 +19381,10 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>p509_EhMdAhgBFxMNFwkMGggLFxcK_RICA</t>
-        </is>
-      </c>
-      <c r="B647" t="inlineStr">
-        <is>
-          <t>AComA</t>
-        </is>
-      </c>
+          <t>p508_BAQfERUEDAQeFQMDBgQDFRAU_LICA</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr"/>
       <c r="C647" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19388,11 +19392,11 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 21.7, 16.9, 16.0, 15.7 mm)</t>
+          <t>Saved successfully (cuts: 12 @ 16.0, 14.5, 13.4, 12.8, 11.4, 11.4, 10.6, 2.1, 1.8, 1.7, 1.5, 1.5 mm)</t>
         </is>
       </c>
       <c r="E647" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -19403,12 +19407,12 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>p511_GAQAGw4NABsbABQVGgQcHx0d</t>
+          <t>p528_BAAEAAINAR8SEwcdFxIaBAMZ</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -19418,11 +19422,11 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 15.4, 15.2, 13.9, 13.4, 13.0, 10.3, 5.1 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 22.1, 7.0, 5.7, 1.7, 1.7 mm)</t>
         </is>
       </c>
       <c r="E648" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -19433,12 +19437,12 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>p513_BA4MDgQHBg4HChIABg4aCgEX</t>
+          <t>p512_FQwfAB4dFw0fDBgCHwAAEBAU</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -19448,11 +19452,11 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 15.7, 10.8, 9.4, 8.3 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 14.5, 13.1, 12.0, 4.3, 2.5, 1.9 mm)</t>
         </is>
       </c>
       <c r="E649" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -19463,14 +19467,10 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>p512_FQwfAB4dFw0fDBgCHwAAEBAU</t>
-        </is>
-      </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>AComA</t>
-        </is>
-      </c>
+          <t>p515_Eg0TDxMHDA0SCwUAEA0PCxYX_RICA</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr"/>
       <c r="C650" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19478,11 +19478,11 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 15.8, 14.2, 13.9, 5.8 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 11.8, 11.6, 10.8, 7.5, 2.1 mm)</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>p514_EwAfEREGEx8SCBYOHAANBBgI_RICA</t>
+          <t>p505_FwQAAxEdHhUNABQNExQCERId</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -19508,11 +19508,11 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 12.8, 11.3, 6.9, 4.2 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 15.8, 15.4, 13.6, 13.3, 13.0, 8.1, 2.3, 2.0 mm)</t>
         </is>
       </c>
       <c r="E651" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -19523,10 +19523,14 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>p515_Eg0TDxMHDA0SCwUAEA0PCxYX_RICA</t>
-        </is>
-      </c>
-      <c r="B652" t="inlineStr"/>
+          <t>p514_EwAfEREGEx8SCBYOHAANBBgI_RICA</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>ICA pcom</t>
+        </is>
+      </c>
       <c r="C652" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19534,11 +19538,11 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 13.1, 13.0, 12.5, 8.0 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 11.0, 10.3, 6.5, 3.7, 2.5, 1.8 mm)</t>
         </is>
       </c>
       <c r="E652" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -19549,12 +19553,12 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>p516_FAQEBBwJCx8WEwMDExgKAAMd_LICA</t>
+          <t>p511_GAQAGw4NABsbABQVGgQcHx0d</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>AComA</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -19564,11 +19568,11 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 9.6, 7.6, 6.2, 5.9, 5.8, 5.8, 5.0 mm)</t>
+          <t>Saved successfully (cuts: 11 @ 13.0, 13.0, 12.8, 12.5, 12.0, 9.5, 4.2, 2.2, 1.8, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E653" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -19579,14 +19583,10 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>p517_BAgfDgUbAQAKABgGHw4bFgYZ_RICA</t>
-        </is>
-      </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>ICA oph</t>
-        </is>
-      </c>
+          <t>p495_AAQAExkGDAQBFw8BAgQcFxwW</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr"/>
       <c r="C654" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19594,11 +19594,11 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 17.2, 12.8, 11.5, 7.5, 7.4, 6.6, 5.7 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 11.5, 8.1, 8.0, 7.7, 7.2, 6.8, 4.4, 3.4, 2.0, 1.5 mm)</t>
         </is>
       </c>
       <c r="E654" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -19609,10 +19609,14 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>p519_EgAeDBUaDAAfCAMdEAACCBAK_LICA</t>
-        </is>
-      </c>
-      <c r="B655" t="inlineStr"/>
+          <t>p516_FAQEBBwJCx8WEwMDExgKAAMd_LICA</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>MCA bif</t>
+        </is>
+      </c>
       <c r="C655" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19620,11 +19624,11 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 18.8, 10.9, 10.5, 7.1, 6.0 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 8.8, 6.5, 5.9, 5.4, 4.9, 4.7, 4.4, 1.6, 1.6 mm)</t>
         </is>
       </c>
       <c r="E655" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -19635,7 +19639,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>p518_ERUeAB4WBg0SCwcbHgAABAEU_RICA</t>
+          <t>p519_EgAeDBUaDAAfCAMdEAACCBAK_LICA</t>
         </is>
       </c>
       <c r="B656" t="inlineStr"/>
@@ -19646,11 +19650,11 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 22.0, 15.0, 13.3, 11.3, 6.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 15.7, 9.2, 8.7, 6.3, 5.6, 3.4, 2.2, 1.9 mm)</t>
         </is>
       </c>
       <c r="E656" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -19661,12 +19665,12 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>p523_GgARAhEaFh8SBgUOAAUEBBYb_RICA</t>
+          <t>p526_EwkTDxUSDAkSCwMVEQkPCxAC_LICA</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>ICA pcom</t>
+          <t>MCA bif</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -19676,11 +19680,11 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 12.2, 11.0, 10.4, 7.9, 4.3, 4.2, 3.8 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.1, 7.5, 6.4, 6.0, 4.9, 4.5, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E657" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -19691,12 +19695,12 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>p527_Eg4ADxEGFh8cFwgOHAUMCgcW</t>
+          <t>p523_GgARAhEaFh8SBgUOAAUEBBYb_RICA</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>PCA P1-P2</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -19706,11 +19710,11 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 11.1, 10.3, 8.5, 3.1, 5.4 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 10.7, 9.1, 8.5, 7.3, 4.2, 2.6, 2.0, 1.8, 1.6 mm)</t>
         </is>
       </c>
       <c r="E658" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -19721,12 +19725,12 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>p526_EwkTDxUSDAkSCwMVEQkPCxAC_LICA</t>
+          <t>p517_BAgfDgUbAQAKABgGHw4bFgYZ_RICA</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -19736,11 +19740,11 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 15.6, 8.1, 7.9, 7.1, 6.2, 5.1 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 14.4, 11.3, 10.1, 6.9, 6.3, 6.1, 5.5, 2.6 mm)</t>
         </is>
       </c>
       <c r="E659" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -19751,14 +19755,10 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>p528_BAAEAAINAR8SEwcdFxIaBAMZ</t>
-        </is>
-      </c>
-      <c r="B660" t="inlineStr">
-        <is>
-          <t>BA tip</t>
-        </is>
-      </c>
+          <t>p533_BhQRCh8eGwINEAUEHRcHBgMN_RICA</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr"/>
       <c r="C660" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19766,11 +19766,11 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 24.6, 7.8, 7.1, 9.5 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 16.4, 15.3, 10.0, 9.3, 9.0, 1.9, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>p525_Ag4BBAINHBINChUKAAQAFgcX_LMCA</t>
+          <t>p536_GBQVAAMWBwYSFg4aFQAdDQAf_LICA</t>
         </is>
       </c>
       <c r="B661" t="inlineStr"/>
@@ -19792,11 +19792,11 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 12.9, 11.7, 8.5, 7.9, 4.7, 4.4 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 16.8, 9.6, 9.5, 9.3, 8.5, 7.5, 2.2, 1.5 mm)</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -19807,14 +19807,10 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>p529_HRQcEhgWBw8ADQsaHBIGCAAW_LICA</t>
-        </is>
-      </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>ICA oph</t>
-        </is>
-      </c>
+          <t>p525_Ag4BBAINHBINChUKAAQAFgcX_LMCA</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr"/>
       <c r="C662" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19822,11 +19818,11 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 15.5, 13.0, 11.6, 9.6, 9.4 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 10.5, 7.7, 7.6, 7.4, 4.1, 3.6, 2.4, 3.4, 1.6, 1.6 mm)</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -19837,14 +19833,10 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>p530_AAgcCR83HgQaEQMRGw8GCioU_LICA</t>
-        </is>
-      </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>MCA bif</t>
-        </is>
-      </c>
+          <t>p518_ERUeAB4WBg0SCwcbHgAABAEU_RICA</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr"/>
       <c r="C663" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19852,7 +19844,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 13.8, 7.1, 6.9, 6.5, 5.4, 5.2, 5.2 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 13.9, 11.8, 11.5, 10.4, 6.5, 9.4, 1.6 mm)</t>
         </is>
       </c>
       <c r="E663" t="n">
@@ -19867,14 +19859,10 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>p532_EwAcCAYNCB8SCw8ZFxsNBBsR_RICA</t>
-        </is>
-      </c>
-      <c r="B664" t="inlineStr">
-        <is>
-          <t>ICA pcom</t>
-        </is>
-      </c>
+          <t>p535_FQ0QEwkLGhUNCQQdCwIGERAU_LICA</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr"/>
       <c r="C664" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19882,11 +19870,11 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 19.4, 13.8, 13.1, 11.4, 8.6 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 12.7, 10.2, 7.2, 5.1, 1.7, 1.7, 1.6 mm)</t>
         </is>
       </c>
       <c r="E664" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -19897,12 +19885,12 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>p531_AAgcCR83HgQaEQMRGw8GCioU_RICA</t>
+          <t>p534_Ag4BEhUcDA4AFgMbAA4dFhAM_RICA</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>MCA bif</t>
+          <t>ICA bif</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -19912,11 +19900,11 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 16.2, 16.0, 8.6, 8.4, 5.8, 5.5 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 19.4, 11.4, 8.8, 5.0, 2.7 mm)</t>
         </is>
       </c>
       <c r="E665" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -19927,10 +19915,14 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>p533_BhQRCh8eGwINEAUEHRcHBgMN_RICA</t>
-        </is>
-      </c>
-      <c r="B666" t="inlineStr"/>
+          <t>p531_AAgcCR83HgQaEQMRGw8GCioU_RICA</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>MCA bif</t>
+        </is>
+      </c>
       <c r="C666" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19938,11 +19930,11 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 18.0, 15.5, 11.0, 10.4, 10.0 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 15.2, 12.7, 8.3, 8.1, 5.2, 4.6, 2.3, 2.1, 2.1, 1.6 mm)</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -19953,10 +19945,14 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>p535_FQ0QEwkLGhUNCQQdCwIGERAU_LICA</t>
-        </is>
-      </c>
-      <c r="B667" t="inlineStr"/>
+          <t>p529_HRQcEhgWBw8ADQsaHBIGCAAW_LICA</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>ICA oph</t>
+        </is>
+      </c>
       <c r="C667" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -19964,11 +19960,11 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 16.5, 14.8, 10.0, 5.5 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 14.6, 11.5, 10.6, 8.7, 8.4, 2.0, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -19979,12 +19975,12 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>p534_Ag4BEhUcDA4AFgMbAA4dFhAM_RICA</t>
+          <t>p532_EwAcCAYNCB8SCw8ZFxsNBBsR_RICA</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>ICA bif</t>
+          <t>ICA pcom</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -19994,11 +19990,11 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 21.4, 13.2, 12.5, 6.8 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 18.1, 11.4, 11.4, 9.2, 8.0, 2.3, 1.9, 1.7, 1.5 mm)</t>
         </is>
       </c>
       <c r="E668" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -20009,10 +20005,14 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>p536_GBQVAAMWBwYSFg4aFQAdDQAf_LICA</t>
-        </is>
-      </c>
-      <c r="B669" t="inlineStr"/>
+          <t>p530_AAgcCR83HgQaEQMRGw8GCioU_LICA</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>MCA bif</t>
+        </is>
+      </c>
       <c r="C669" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -20020,11 +20020,11 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 18.3, 10.5, 10.0, 10.0, 9.0, 8.2 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 13.1, 6.8, 6.2, 5.7, 4.9, 4.7, 4.4, 1.5 mm)</t>
         </is>
       </c>
       <c r="E669" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>p538_EgAAAxUSExUNBBQNFxsPERcZ_LICA</t>
+          <t>p544_BBIbFR8bDBIaEQkcBhIHERoL_RICA</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -20050,7 +20050,7 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 17.6, 12.6, 12.0, 10.4, 7.7, 6.2, 3.6 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 14.7, 12.8, 11.9, 11.1, 8.4, 2.4, 1.4 mm)</t>
         </is>
       </c>
       <c r="E670" t="n">
@@ -20065,10 +20065,14 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>p541_AAgRAAIMLQYGDAEBHQ8xNzw7MQ==_Acom</t>
-        </is>
-      </c>
-      <c r="B671" t="inlineStr"/>
+          <t>p538_EgAAAxUSExUNBBQNFxsPERcZ_LICA</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>AComA</t>
+        </is>
+      </c>
       <c r="C671" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -20076,11 +20080,11 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 18.4, 17.9, 17.0, 12.5, 10.2, 7.8 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 15.8, 11.4, 10.7, 8.5, 7.3, 5.1, 2.9, 1.7, 1.5, 1.4 mm)</t>
         </is>
       </c>
       <c r="E671" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -20106,11 +20110,11 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 15.4, 13.2, 13.2, 11.5, 11.0, 8.6, 8.5 mm)</t>
+          <t>Saved successfully (cuts: 11 @ 12.4, 12.2, 12.0, 10.8, 10.3, 8.1, 7.8, 3.2, 1.7, 1.6, 1.5 mm)</t>
         </is>
       </c>
       <c r="E672" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -20121,12 +20125,12 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>p544_BBIbFR8bDBIaEQkcBhIHERoL_RICA</t>
+          <t>p549_AwAeAA4JHgAABAoOAQACBAYZ_TB</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>AComA</t>
+          <t>BA tip</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -20136,11 +20140,11 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 16.4, 15.0, 13.3, 11.4, 9.4 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 25.4, 16.7, 13.7, 13.5, 12.6, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E673" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -20151,7 +20155,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>p547_Eg4cDxUeGwQNCggBFxcHABcX_RICA</t>
+          <t>p548_FAAtDQUSDAAsCRMVFgAxCQAC_LICA</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -20166,11 +20170,11 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.9, 13.9, 12.7, 12.4, 7.9 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 14.3, 12.8, 11.2, 7.5, 7.0, 3.5, 1.7 mm)</t>
         </is>
       </c>
       <c r="E674" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -20181,14 +20185,10 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>p548_FAAtDQUSDAAsCRMVFgAxCQAC_LICA</t>
-        </is>
-      </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>ICA cav</t>
-        </is>
-      </c>
+          <t>p541_AAgRAAIMLQYGDAEBHQ8xNzw7MQ==_Acom</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr"/>
       <c r="C675" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -20196,11 +20196,11 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 15.3, 14.0, 13.7, 7.9, 5.6, 4.1 mm)</t>
+          <t>Saved successfully (cuts: 10 @ 16.9, 16.3, 15.2, 12.0, 9.8, 7.0, 1.8, 1.7, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -20226,11 +20226,11 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 7 @ 18.4, 18.3, 16.5, 12.4, 12.3, 11.9, 11.4 mm)</t>
+          <t>Saved successfully (cuts: 9 @ 19.7, 17.6, 15.7, 11.7, 11.5, 11.0, 10.1, 10.0, 1.6 mm)</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -20241,12 +20241,12 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>p549_AwAeAA4JHgAABAoOAQACBAYZ_TB</t>
+          <t>p550_Gw4aDwQHAhENCg4BBg4eFR4X_LICA</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>BA tip</t>
+          <t>ICA oph</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 26.1, 19.1, 16.6, 14.9, 14.3 mm)</t>
+          <t>Saved successfully (cuts: 5 @ 13.5, 11.6, 10.0, 7.2, 1.8 mm)</t>
         </is>
       </c>
       <c r="E677" t="n">
@@ -20271,12 +20271,12 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>p550_Gw4aDwQHAhENCg4BBg4eFR4X_LICA</t>
+          <t>p555_AAQAExkGDAQBFw8BAgQcFxwW_TB</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>ICA oph</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -20286,11 +20286,11 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 14.2, 13.7, 11.3, 7.4 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 18.0, 15.8, 15.7, 11.2, 10.5, 1.6, 1.6, 1.4 mm)</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>p552_AwkTAxEGGx8bBAQOHAgdDRQa_RICA</t>
+          <t>p553_FxMTDxQCFwAdGxQOHAUEABQW_RICA</t>
         </is>
       </c>
       <c r="B679" t="inlineStr"/>
@@ -20312,11 +20312,11 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.5, 12.2, 10.5, 10.2, 9.3 mm)</t>
+          <t>Saved successfully (cuts: 7 @ 12.3, 10.2, 9.8, 8.1, 8.0, 2.1, 2.0 mm)</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -20327,10 +20327,14 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>p551_EwkdAxESDAkcBwcVEQkBBxQC_RMCA</t>
-        </is>
-      </c>
-      <c r="B680" t="inlineStr"/>
+          <t>p547_Eg4cDxUeGwQNCggBFxcHABcX_RICA</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>ICA cav</t>
+        </is>
+      </c>
       <c r="C680" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -20338,7 +20342,7 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 6 @ 18.5, 11.3, 11.0, 10.7, 10.0, 8.7 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 13.9, 12.8, 12.3, 11.3, 7.5, 2.2 mm)</t>
         </is>
       </c>
       <c r="E680" t="n">
@@ -20353,14 +20357,10 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>p554_AwQAFxEBAR8WFxAOGxIdAAcO_RICA</t>
-        </is>
-      </c>
-      <c r="B681" t="inlineStr">
-        <is>
-          <t>MCA M1</t>
-        </is>
-      </c>
+          <t>p552_AwkTAxEGGx8bBAQOHAgdDRQa_RICA</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr"/>
       <c r="C681" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -20368,11 +20368,11 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 4 @ 15.1, 14.4, 14.3, 7.2 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 12.7, 11.0, 9.4, 9.0, 8.4, 2.2, 1.6, 1.6 mm)</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -20383,10 +20383,14 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>p553_FxMTDxQCFwAdGxQOHAUEABQW_RICA</t>
-        </is>
-      </c>
-      <c r="B682" t="inlineStr"/>
+          <t>p554_AwQAFxEBAR8WFxAOGxIdAAcO_RICA</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>MCA M1</t>
+        </is>
+      </c>
       <c r="C682" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -20394,11 +20398,11 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 14.7, 12.2, 10.4, 8.6, 8.4 mm)</t>
+          <t>Saved successfully (cuts: 6 @ 13.5, 13.5, 11.1, 6.2, 2.9, 2.7 mm)</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -20409,14 +20413,10 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>p555_AAQAExkGDAQBFw8BAgQcFxwW_TB</t>
-        </is>
-      </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
+          <t>p551_EwkdAxESDAkcBwcVEQkBBxQC_RMCA</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr"/>
       <c r="C683" t="inlineStr">
         <is>
           <t>Saved</t>
@@ -20424,11 +20424,11 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Saved successfully (cuts: 5 @ 19.4, 16.8, 16.6, 12.8, 12.4 mm)</t>
+          <t>Saved successfully (cuts: 8 @ 17.0, 10.3, 10.1, 9.6, 9.1, 7.4, 2.0, 1.5 mm)</t>
         </is>
       </c>
       <c r="E683" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
